--- a/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/monthly_bootstrap_combined_data_costs_users.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/monthly_bootstrap_combined_data_costs_users.xlsx
@@ -421,34 +421,34 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>267.821</v>
+        <v>271.688</v>
       </c>
       <c r="C2">
-        <v>5.834</v>
+        <v>6.249</v>
       </c>
       <c r="D2">
-        <v>2.415</v>
+        <v>2.5</v>
       </c>
       <c r="E2">
-        <v>0.076</v>
+        <v>0.079</v>
       </c>
       <c r="F2">
-        <v>263.181</v>
+        <v>266.884</v>
       </c>
       <c r="G2">
-        <v>272.649</v>
+        <v>276.683</v>
       </c>
       <c r="H2">
-        <v>263.067</v>
+        <v>266.827</v>
       </c>
       <c r="I2">
-        <v>272.392</v>
+        <v>276.449</v>
       </c>
       <c r="J2">
-        <v>263.344</v>
+        <v>267.022</v>
       </c>
       <c r="K2">
-        <v>272.669</v>
+        <v>276.644</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -461,34 +461,34 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>177.949</v>
+        <v>182.813</v>
       </c>
       <c r="C3">
-        <v>3.48</v>
+        <v>3.953</v>
       </c>
       <c r="D3">
-        <v>1.866</v>
+        <v>1.988</v>
       </c>
       <c r="E3">
-        <v>0.059</v>
+        <v>0.063</v>
       </c>
       <c r="F3">
-        <v>174.315</v>
+        <v>178.942</v>
       </c>
       <c r="G3">
-        <v>181.628</v>
+        <v>186.737</v>
       </c>
       <c r="H3">
-        <v>174.101</v>
+        <v>178.639</v>
       </c>
       <c r="I3">
-        <v>181.606</v>
+        <v>186.64</v>
       </c>
       <c r="J3">
-        <v>174.314</v>
+        <v>179.013</v>
       </c>
       <c r="K3">
-        <v>181.818</v>
+        <v>187.013</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -501,34 +501,34 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>117.42</v>
+        <v>121.591</v>
       </c>
       <c r="C4">
-        <v>2.387</v>
+        <v>2.545</v>
       </c>
       <c r="D4">
-        <v>1.545</v>
+        <v>1.595</v>
       </c>
       <c r="E4">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="F4">
-        <v>114.43</v>
+        <v>118.501</v>
       </c>
       <c r="G4">
-        <v>120.486</v>
+        <v>124.756</v>
       </c>
       <c r="H4">
-        <v>114.281</v>
+        <v>118.337</v>
       </c>
       <c r="I4">
-        <v>120.452</v>
+        <v>124.657</v>
       </c>
       <c r="J4">
-        <v>114.425</v>
+        <v>118.562</v>
       </c>
       <c r="K4">
-        <v>120.596</v>
+        <v>124.882</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -541,34 +541,34 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>83.565</v>
+        <v>86.646</v>
       </c>
       <c r="C5">
-        <v>3.16</v>
+        <v>3.227</v>
       </c>
       <c r="D5">
-        <v>1.778</v>
+        <v>1.796</v>
       </c>
       <c r="E5">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="F5">
-        <v>80.09399999999999</v>
+        <v>83.14100000000001</v>
       </c>
       <c r="G5">
-        <v>87.063</v>
+        <v>90.182</v>
       </c>
       <c r="H5">
-        <v>79.667</v>
+        <v>82.693</v>
       </c>
       <c r="I5">
-        <v>86.785</v>
+        <v>89.92400000000001</v>
       </c>
       <c r="J5">
-        <v>80.35899999999999</v>
+        <v>83.383</v>
       </c>
       <c r="K5">
-        <v>87.477</v>
+        <v>90.614</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -581,34 +581,34 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>64.19799999999999</v>
+        <v>66.613</v>
       </c>
       <c r="C6">
-        <v>1.206</v>
+        <v>1.296</v>
       </c>
       <c r="D6">
-        <v>1.098</v>
+        <v>1.138</v>
       </c>
       <c r="E6">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="F6">
-        <v>62.096</v>
+        <v>64.44199999999999</v>
       </c>
       <c r="G6">
-        <v>66.401</v>
+        <v>68.904</v>
       </c>
       <c r="H6">
-        <v>61.978</v>
+        <v>64.3</v>
       </c>
       <c r="I6">
-        <v>66.39100000000001</v>
+        <v>68.89100000000001</v>
       </c>
       <c r="J6">
-        <v>62.055</v>
+        <v>64.39400000000001</v>
       </c>
       <c r="K6">
-        <v>66.468</v>
+        <v>68.985</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -621,34 +621,34 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>52.251</v>
+        <v>54.278</v>
       </c>
       <c r="C7">
-        <v>1.008</v>
+        <v>1.103</v>
       </c>
       <c r="D7">
-        <v>1.004</v>
+        <v>1.05</v>
       </c>
       <c r="E7">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="F7">
-        <v>50.243</v>
+        <v>52.181</v>
       </c>
       <c r="G7">
-        <v>54.179</v>
+        <v>56.298</v>
       </c>
       <c r="H7">
-        <v>50.196</v>
+        <v>52.134</v>
       </c>
       <c r="I7">
-        <v>54.118</v>
+        <v>56.243</v>
       </c>
       <c r="J7">
-        <v>50.345</v>
+        <v>52.274</v>
       </c>
       <c r="K7">
-        <v>54.266</v>
+        <v>56.383</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -661,34 +661,34 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>45.048</v>
+        <v>46.702</v>
       </c>
       <c r="C8">
-        <v>0.914</v>
+        <v>0.997</v>
       </c>
       <c r="D8">
-        <v>0.956</v>
+        <v>0.999</v>
       </c>
       <c r="E8">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="F8">
-        <v>43.19</v>
+        <v>44.762</v>
       </c>
       <c r="G8">
-        <v>46.937</v>
+        <v>48.676</v>
       </c>
       <c r="H8">
-        <v>43.173</v>
+        <v>44.758</v>
       </c>
       <c r="I8">
-        <v>46.941</v>
+        <v>48.691</v>
       </c>
       <c r="J8">
-        <v>43.17</v>
+        <v>44.73</v>
       </c>
       <c r="K8">
-        <v>46.938</v>
+        <v>48.663</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -701,34 +701,34 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>38.963</v>
+        <v>40.493</v>
       </c>
       <c r="C9">
-        <v>0.738</v>
+        <v>0.824</v>
       </c>
       <c r="D9">
-        <v>0.859</v>
+        <v>0.908</v>
       </c>
       <c r="E9">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
       <c r="F9">
-        <v>37.209</v>
+        <v>38.641</v>
       </c>
       <c r="G9">
-        <v>40.575</v>
+        <v>42.199</v>
       </c>
       <c r="H9">
-        <v>37.185</v>
+        <v>38.646</v>
       </c>
       <c r="I9">
-        <v>40.607</v>
+        <v>42.202</v>
       </c>
       <c r="J9">
-        <v>37.248</v>
+        <v>38.71</v>
       </c>
       <c r="K9">
-        <v>40.669</v>
+        <v>42.267</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -741,34 +741,34 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>34.93</v>
+        <v>36.168</v>
       </c>
       <c r="C10">
-        <v>0.599</v>
+        <v>0.65</v>
       </c>
       <c r="D10">
-        <v>0.774</v>
+        <v>0.806</v>
       </c>
       <c r="E10">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="F10">
-        <v>33.342</v>
+        <v>34.518</v>
       </c>
       <c r="G10">
-        <v>36.376</v>
+        <v>37.678</v>
       </c>
       <c r="H10">
-        <v>33.302</v>
+        <v>34.458</v>
       </c>
       <c r="I10">
-        <v>36.382</v>
+        <v>37.656</v>
       </c>
       <c r="J10">
-        <v>33.407</v>
+        <v>34.609</v>
       </c>
       <c r="K10">
-        <v>36.487</v>
+        <v>37.808</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -781,34 +781,34 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>33.678</v>
+        <v>34.853</v>
       </c>
       <c r="C11">
-        <v>0.581</v>
+        <v>0.631</v>
       </c>
       <c r="D11">
-        <v>0.762</v>
+        <v>0.794</v>
       </c>
       <c r="E11">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="F11">
-        <v>32.139</v>
+        <v>33.252</v>
       </c>
       <c r="G11">
-        <v>35.126</v>
+        <v>36.365</v>
       </c>
       <c r="H11">
-        <v>32.04</v>
+        <v>33.184</v>
       </c>
       <c r="I11">
-        <v>35.163</v>
+        <v>36.451</v>
       </c>
       <c r="J11">
-        <v>32.148</v>
+        <v>33.211</v>
       </c>
       <c r="K11">
-        <v>35.271</v>
+        <v>36.477</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -821,34 +821,34 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>31.284</v>
+        <v>32.405</v>
       </c>
       <c r="C12">
-        <v>0.628</v>
+        <v>0.671</v>
       </c>
       <c r="D12">
-        <v>0.793</v>
+        <v>0.819</v>
       </c>
       <c r="E12">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="F12">
-        <v>29.788</v>
+        <v>30.861</v>
       </c>
       <c r="G12">
-        <v>32.895</v>
+        <v>34.072</v>
       </c>
       <c r="H12">
-        <v>29.765</v>
+        <v>30.815</v>
       </c>
       <c r="I12">
-        <v>32.819</v>
+        <v>34.001</v>
       </c>
       <c r="J12">
-        <v>29.807</v>
+        <v>30.871</v>
       </c>
       <c r="K12">
-        <v>32.861</v>
+        <v>34.057</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -861,34 +861,34 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>32.263</v>
+        <v>33.327</v>
       </c>
       <c r="C13">
-        <v>0.571</v>
+        <v>0.605</v>
       </c>
       <c r="D13">
-        <v>0.756</v>
+        <v>0.778</v>
       </c>
       <c r="E13">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="F13">
-        <v>30.785</v>
+        <v>31.809</v>
       </c>
       <c r="G13">
-        <v>33.749</v>
+        <v>34.857</v>
       </c>
       <c r="H13">
-        <v>30.738</v>
+        <v>31.752</v>
       </c>
       <c r="I13">
-        <v>33.696</v>
+        <v>34.8</v>
       </c>
       <c r="J13">
-        <v>30.834</v>
+        <v>31.86</v>
       </c>
       <c r="K13">
-        <v>33.792</v>
+        <v>34.908</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -901,34 +901,34 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>27.58</v>
+        <v>28.569</v>
       </c>
       <c r="C14">
-        <v>0.444</v>
+        <v>0.48</v>
       </c>
       <c r="D14">
-        <v>0.666</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="E14">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="F14">
-        <v>26.218</v>
+        <v>27.153</v>
       </c>
       <c r="G14">
-        <v>28.829</v>
+        <v>29.869</v>
       </c>
       <c r="H14">
-        <v>26.153</v>
+        <v>27.063</v>
       </c>
       <c r="I14">
-        <v>28.831</v>
+        <v>29.858</v>
       </c>
       <c r="J14">
-        <v>26.273</v>
+        <v>27.222</v>
       </c>
       <c r="K14">
-        <v>28.95</v>
+        <v>30.017</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -941,34 +941,34 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>27.799</v>
+        <v>28.708</v>
       </c>
       <c r="C15">
-        <v>0.444</v>
+        <v>0.47</v>
       </c>
       <c r="D15">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E15">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="F15">
-        <v>26.474</v>
+        <v>27.349</v>
       </c>
       <c r="G15">
-        <v>29.085</v>
+        <v>30.036</v>
       </c>
       <c r="H15">
-        <v>26.424</v>
+        <v>27.31</v>
       </c>
       <c r="I15">
-        <v>29.113</v>
+        <v>30.059</v>
       </c>
       <c r="J15">
-        <v>26.466</v>
+        <v>27.341</v>
       </c>
       <c r="K15">
-        <v>29.155</v>
+        <v>30.091</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -981,34 +981,34 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>25.861</v>
+        <v>26.801</v>
       </c>
       <c r="C16">
-        <v>0.482</v>
+        <v>0.519</v>
       </c>
       <c r="D16">
-        <v>0.694</v>
+        <v>0.721</v>
       </c>
       <c r="E16">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="F16">
-        <v>24.502</v>
+        <v>25.393</v>
       </c>
       <c r="G16">
-        <v>27.223</v>
+        <v>28.217</v>
       </c>
       <c r="H16">
-        <v>24.43</v>
+        <v>25.301</v>
       </c>
       <c r="I16">
-        <v>27.149</v>
+        <v>28.134</v>
       </c>
       <c r="J16">
-        <v>24.574</v>
+        <v>25.472</v>
       </c>
       <c r="K16">
-        <v>27.294</v>
+        <v>28.306</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1021,34 +1021,34 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>25.682</v>
+        <v>26.552</v>
       </c>
       <c r="C17">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="D17">
-        <v>0.7</v>
+        <v>0.721</v>
       </c>
       <c r="E17">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="F17">
-        <v>24.291</v>
+        <v>25.117</v>
       </c>
       <c r="G17">
-        <v>27.034</v>
+        <v>27.945</v>
       </c>
       <c r="H17">
-        <v>24.277</v>
+        <v>25.096</v>
       </c>
       <c r="I17">
-        <v>27.016</v>
+        <v>27.94</v>
       </c>
       <c r="J17">
-        <v>24.329</v>
+        <v>25.143</v>
       </c>
       <c r="K17">
-        <v>27.068</v>
+        <v>27.987</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1061,34 +1061,34 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>25.284</v>
+        <v>26.14</v>
       </c>
       <c r="C18">
-        <v>0.501</v>
+        <v>0.527</v>
       </c>
       <c r="D18">
-        <v>0.708</v>
+        <v>0.726</v>
       </c>
       <c r="E18">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="F18">
-        <v>23.867</v>
+        <v>24.687</v>
       </c>
       <c r="G18">
-        <v>26.641</v>
+        <v>27.531</v>
       </c>
       <c r="H18">
-        <v>23.83</v>
+        <v>24.647</v>
       </c>
       <c r="I18">
-        <v>26.638</v>
+        <v>27.527</v>
       </c>
       <c r="J18">
-        <v>23.9</v>
+        <v>24.722</v>
       </c>
       <c r="K18">
-        <v>26.709</v>
+        <v>27.602</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1101,34 +1101,34 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>23.273</v>
+        <v>24.068</v>
       </c>
       <c r="C19">
-        <v>0.443</v>
+        <v>0.467</v>
       </c>
       <c r="D19">
-        <v>0.666</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="E19">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="F19">
-        <v>22.01</v>
+        <v>22.771</v>
       </c>
       <c r="G19">
-        <v>24.619</v>
+        <v>25.45</v>
       </c>
       <c r="H19">
-        <v>21.943</v>
+        <v>22.69</v>
       </c>
       <c r="I19">
-        <v>24.548</v>
+        <v>25.392</v>
       </c>
       <c r="J19">
-        <v>22.04</v>
+        <v>22.787</v>
       </c>
       <c r="K19">
-        <v>24.644</v>
+        <v>25.488</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1141,34 +1141,34 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>22.424</v>
+        <v>23.23</v>
       </c>
       <c r="C20">
-        <v>0.459</v>
+        <v>0.486</v>
       </c>
       <c r="D20">
-        <v>0.677</v>
+        <v>0.697</v>
       </c>
       <c r="E20">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="F20">
-        <v>21.099</v>
+        <v>21.866</v>
       </c>
       <c r="G20">
-        <v>23.754</v>
+        <v>24.6</v>
       </c>
       <c r="H20">
-        <v>21.064</v>
+        <v>21.825</v>
       </c>
       <c r="I20">
-        <v>23.699</v>
+        <v>24.534</v>
       </c>
       <c r="J20">
-        <v>21.152</v>
+        <v>21.929</v>
       </c>
       <c r="K20">
-        <v>23.787</v>
+        <v>24.637</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1181,34 +1181,34 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>21.902</v>
+        <v>22.637</v>
       </c>
       <c r="C21">
-        <v>0.409</v>
+        <v>0.436</v>
       </c>
       <c r="D21">
-        <v>0.639</v>
+        <v>0.66</v>
       </c>
       <c r="E21">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="F21">
-        <v>20.609</v>
+        <v>21.297</v>
       </c>
       <c r="G21">
-        <v>23.114</v>
+        <v>23.886</v>
       </c>
       <c r="H21">
-        <v>20.507</v>
+        <v>21.185</v>
       </c>
       <c r="I21">
-        <v>23.111</v>
+        <v>23.857</v>
       </c>
       <c r="J21">
-        <v>20.652</v>
+        <v>21.371</v>
       </c>
       <c r="K21">
-        <v>23.257</v>
+        <v>24.043</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>21.103</v>
+        <v>21.837</v>
       </c>
       <c r="C22">
-        <v>0.448</v>
+        <v>0.474</v>
       </c>
       <c r="D22">
-        <v>0.669</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="E22">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="F22">
-        <v>19.78</v>
+        <v>20.474</v>
       </c>
       <c r="G22">
-        <v>22.403</v>
+        <v>23.172</v>
       </c>
       <c r="H22">
-        <v>19.713</v>
+        <v>20.386</v>
       </c>
       <c r="I22">
-        <v>22.374</v>
+        <v>23.149</v>
       </c>
       <c r="J22">
-        <v>19.821</v>
+        <v>20.511</v>
       </c>
       <c r="K22">
-        <v>22.482</v>
+        <v>23.274</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1261,34 +1261,34 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>19.384</v>
+        <v>20.043</v>
       </c>
       <c r="C23">
-        <v>0.354</v>
+        <v>0.373</v>
       </c>
       <c r="D23">
-        <v>0.595</v>
+        <v>0.61</v>
       </c>
       <c r="E23">
         <v>0.019</v>
       </c>
       <c r="F23">
-        <v>18.229</v>
+        <v>18.86</v>
       </c>
       <c r="G23">
-        <v>20.562</v>
+        <v>21.253</v>
       </c>
       <c r="H23">
-        <v>18.206</v>
+        <v>18.808</v>
       </c>
       <c r="I23">
-        <v>20.536</v>
+        <v>21.233</v>
       </c>
       <c r="J23">
-        <v>18.244</v>
+        <v>18.866</v>
       </c>
       <c r="K23">
-        <v>20.574</v>
+        <v>21.291</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1301,34 +1301,34 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>19.233</v>
+        <v>19.88</v>
       </c>
       <c r="C24">
-        <v>0.422</v>
+        <v>0.436</v>
       </c>
       <c r="D24">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="E24">
         <v>0.021</v>
       </c>
       <c r="F24">
-        <v>17.91</v>
+        <v>18.537</v>
       </c>
       <c r="G24">
-        <v>20.456</v>
+        <v>21.124</v>
       </c>
       <c r="H24">
-        <v>17.946</v>
+        <v>18.573</v>
       </c>
       <c r="I24">
-        <v>20.484</v>
+        <v>21.165</v>
       </c>
       <c r="J24">
-        <v>17.932</v>
+        <v>18.545</v>
       </c>
       <c r="K24">
-        <v>20.47</v>
+        <v>21.138</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1341,34 +1341,34 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>17.46</v>
+        <v>18.081</v>
       </c>
       <c r="C25">
-        <v>0.315</v>
+        <v>0.332</v>
       </c>
       <c r="D25">
-        <v>0.5610000000000001</v>
+        <v>0.576</v>
       </c>
       <c r="E25">
         <v>0.018</v>
       </c>
       <c r="F25">
-        <v>16.349</v>
+        <v>16.945</v>
       </c>
       <c r="G25">
-        <v>18.55</v>
+        <v>19.203</v>
       </c>
       <c r="H25">
-        <v>16.436</v>
+        <v>16.993</v>
       </c>
       <c r="I25">
-        <v>18.532</v>
+        <v>19.174</v>
       </c>
       <c r="J25">
-        <v>16.378</v>
+        <v>16.98</v>
       </c>
       <c r="K25">
-        <v>18.474</v>
+        <v>19.161</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="B26">
-        <v>290.284</v>
+        <v>295.616</v>
       </c>
       <c r="C26">
-        <v>6.85</v>
+        <v>6.471</v>
       </c>
       <c r="D26">
-        <v>2.617</v>
+        <v>2.544</v>
       </c>
       <c r="E26">
-        <v>0.083</v>
+        <v>0.08</v>
       </c>
       <c r="F26">
-        <v>285.421</v>
+        <v>290.896</v>
       </c>
       <c r="G26">
-        <v>295.68</v>
+        <v>300.868</v>
       </c>
       <c r="H26">
-        <v>285.35</v>
+        <v>290.826</v>
       </c>
       <c r="I26">
-        <v>295.693</v>
+        <v>300.924</v>
       </c>
       <c r="J26">
-        <v>285.142</v>
+        <v>290.574</v>
       </c>
       <c r="K26">
-        <v>295.484</v>
+        <v>300.672</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1421,34 +1421,34 @@
         <v>2</v>
       </c>
       <c r="B27">
-        <v>187.397</v>
+        <v>191.34</v>
       </c>
       <c r="C27">
-        <v>3.812</v>
+        <v>3.751</v>
       </c>
       <c r="D27">
-        <v>1.952</v>
+        <v>1.937</v>
       </c>
       <c r="E27">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="F27">
-        <v>183.316</v>
+        <v>187.277</v>
       </c>
       <c r="G27">
-        <v>190.969</v>
+        <v>194.869</v>
       </c>
       <c r="H27">
-        <v>183.26</v>
+        <v>187.315</v>
       </c>
       <c r="I27">
-        <v>190.876</v>
+        <v>194.882</v>
       </c>
       <c r="J27">
-        <v>183.664</v>
+        <v>187.531</v>
       </c>
       <c r="K27">
-        <v>191.28</v>
+        <v>195.098</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1461,34 +1461,34 @@
         <v>3</v>
       </c>
       <c r="B28">
-        <v>123.894</v>
+        <v>127.49</v>
       </c>
       <c r="C28">
-        <v>2.941</v>
+        <v>2.798</v>
       </c>
       <c r="D28">
-        <v>1.715</v>
+        <v>1.673</v>
       </c>
       <c r="E28">
-        <v>0.054</v>
+        <v>0.053</v>
       </c>
       <c r="F28">
-        <v>120.448</v>
+        <v>124.098</v>
       </c>
       <c r="G28">
-        <v>127.171</v>
+        <v>130.655</v>
       </c>
       <c r="H28">
-        <v>120.446</v>
+        <v>124.07</v>
       </c>
       <c r="I28">
-        <v>127.184</v>
+        <v>130.675</v>
       </c>
       <c r="J28">
-        <v>120.521</v>
+        <v>124.191</v>
       </c>
       <c r="K28">
-        <v>127.259</v>
+        <v>130.796</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1501,34 +1501,34 @@
         <v>4</v>
       </c>
       <c r="B29">
-        <v>87.569</v>
+        <v>90.39400000000001</v>
       </c>
       <c r="C29">
-        <v>2.779</v>
+        <v>2.76</v>
       </c>
       <c r="D29">
-        <v>1.667</v>
+        <v>1.661</v>
       </c>
       <c r="E29">
         <v>0.053</v>
       </c>
       <c r="F29">
-        <v>84.241</v>
+        <v>87.074</v>
       </c>
       <c r="G29">
-        <v>90.77500000000001</v>
+        <v>93.587</v>
       </c>
       <c r="H29">
-        <v>83.99299999999999</v>
+        <v>86.904</v>
       </c>
       <c r="I29">
-        <v>90.521</v>
+        <v>93.39</v>
       </c>
       <c r="J29">
-        <v>84.556</v>
+        <v>87.334</v>
       </c>
       <c r="K29">
-        <v>91.084</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1541,34 +1541,34 @@
         <v>5</v>
       </c>
       <c r="B30">
-        <v>68.077</v>
+        <v>70.218</v>
       </c>
       <c r="C30">
-        <v>1.319</v>
+        <v>1.369</v>
       </c>
       <c r="D30">
-        <v>1.149</v>
+        <v>1.17</v>
       </c>
       <c r="E30">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
       <c r="F30">
-        <v>65.782</v>
+        <v>67.88200000000001</v>
       </c>
       <c r="G30">
-        <v>70.28400000000001</v>
+        <v>72.46899999999999</v>
       </c>
       <c r="H30">
-        <v>65.759</v>
+        <v>67.80200000000001</v>
       </c>
       <c r="I30">
-        <v>70.239</v>
+        <v>72.387</v>
       </c>
       <c r="J30">
-        <v>65.871</v>
+        <v>68.006</v>
       </c>
       <c r="K30">
-        <v>70.351</v>
+        <v>72.59099999999999</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1581,34 +1581,34 @@
         <v>6</v>
       </c>
       <c r="B31">
-        <v>55.067</v>
+        <v>56.836</v>
       </c>
       <c r="C31">
-        <v>1.042</v>
+        <v>1.081</v>
       </c>
       <c r="D31">
-        <v>1.021</v>
+        <v>1.04</v>
       </c>
       <c r="E31">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="F31">
-        <v>53.146</v>
+        <v>54.876</v>
       </c>
       <c r="G31">
-        <v>57.148</v>
+        <v>58.952</v>
       </c>
       <c r="H31">
-        <v>53.2</v>
+        <v>54.874</v>
       </c>
       <c r="I31">
-        <v>57.188</v>
+        <v>59.028</v>
       </c>
       <c r="J31">
-        <v>53.027</v>
+        <v>54.721</v>
       </c>
       <c r="K31">
-        <v>57.014</v>
+        <v>58.875</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -1621,10 +1621,10 @@
         <v>7</v>
       </c>
       <c r="B32">
-        <v>47.926</v>
+        <v>49.298</v>
       </c>
       <c r="C32">
-        <v>1.003</v>
+        <v>1.004</v>
       </c>
       <c r="D32">
         <v>1.002</v>
@@ -1633,22 +1633,22 @@
         <v>0.032</v>
       </c>
       <c r="F32">
-        <v>46.045</v>
+        <v>47.407</v>
       </c>
       <c r="G32">
-        <v>49.971</v>
+        <v>51.334</v>
       </c>
       <c r="H32">
-        <v>46.023</v>
+        <v>47.414</v>
       </c>
       <c r="I32">
-        <v>49.927</v>
+        <v>51.277</v>
       </c>
       <c r="J32">
-        <v>46.007</v>
+        <v>47.391</v>
       </c>
       <c r="K32">
-        <v>49.911</v>
+        <v>51.255</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -1661,34 +1661,34 @@
         <v>8</v>
       </c>
       <c r="B33">
-        <v>41.748</v>
+        <v>42.955</v>
       </c>
       <c r="C33">
-        <v>0.926</v>
+        <v>0.928</v>
       </c>
       <c r="D33">
-        <v>0.962</v>
+        <v>0.964</v>
       </c>
       <c r="E33">
         <v>0.03</v>
       </c>
       <c r="F33">
-        <v>39.896</v>
+        <v>41.092</v>
       </c>
       <c r="G33">
-        <v>43.667</v>
+        <v>44.869</v>
       </c>
       <c r="H33">
-        <v>39.851</v>
+        <v>41.033</v>
       </c>
       <c r="I33">
-        <v>43.517</v>
+        <v>44.763</v>
       </c>
       <c r="J33">
-        <v>40.012</v>
+        <v>41.171</v>
       </c>
       <c r="K33">
-        <v>43.678</v>
+        <v>44.902</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -1701,34 +1701,34 @@
         <v>9</v>
       </c>
       <c r="B34">
-        <v>37.389</v>
+        <v>38.388</v>
       </c>
       <c r="C34">
-        <v>0.789</v>
+        <v>0.779</v>
       </c>
       <c r="D34">
-        <v>0.888</v>
+        <v>0.882</v>
       </c>
       <c r="E34">
         <v>0.028</v>
       </c>
       <c r="F34">
-        <v>35.614</v>
+        <v>36.625</v>
       </c>
       <c r="G34">
-        <v>39.096</v>
+        <v>40.084</v>
       </c>
       <c r="H34">
-        <v>35.694</v>
+        <v>36.743</v>
       </c>
       <c r="I34">
-        <v>39.103</v>
+        <v>40.151</v>
       </c>
       <c r="J34">
-        <v>35.64</v>
+        <v>36.591</v>
       </c>
       <c r="K34">
-        <v>39.05</v>
+        <v>39.999</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -1741,34 +1741,34 @@
         <v>10</v>
       </c>
       <c r="B35">
-        <v>35.92</v>
+        <v>36.886</v>
       </c>
       <c r="C35">
-        <v>0.732</v>
+        <v>0.751</v>
       </c>
       <c r="D35">
-        <v>0.856</v>
+        <v>0.866</v>
       </c>
       <c r="E35">
         <v>0.027</v>
       </c>
       <c r="F35">
-        <v>34.281</v>
+        <v>35.23</v>
       </c>
       <c r="G35">
-        <v>37.635</v>
+        <v>38.627</v>
       </c>
       <c r="H35">
-        <v>34.185</v>
+        <v>35.202</v>
       </c>
       <c r="I35">
-        <v>37.591</v>
+        <v>38.59</v>
       </c>
       <c r="J35">
-        <v>34.287</v>
+        <v>35.225</v>
       </c>
       <c r="K35">
-        <v>37.693</v>
+        <v>38.613</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -1781,34 +1781,34 @@
         <v>11</v>
       </c>
       <c r="B36">
-        <v>33.59</v>
+        <v>34.472</v>
       </c>
       <c r="C36">
-        <v>0.799</v>
+        <v>0.77</v>
       </c>
       <c r="D36">
-        <v>0.894</v>
+        <v>0.877</v>
       </c>
       <c r="E36">
         <v>0.028</v>
       </c>
       <c r="F36">
-        <v>31.905</v>
+        <v>32.823</v>
       </c>
       <c r="G36">
-        <v>35.409</v>
+        <v>36.262</v>
       </c>
       <c r="H36">
-        <v>31.788</v>
+        <v>32.653</v>
       </c>
       <c r="I36">
-        <v>35.433</v>
+        <v>36.228</v>
       </c>
       <c r="J36">
-        <v>31.814</v>
+        <v>32.787</v>
       </c>
       <c r="K36">
-        <v>35.459</v>
+        <v>36.362</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -1821,34 +1821,34 @@
         <v>12</v>
       </c>
       <c r="B37">
-        <v>34.704</v>
+        <v>35.508</v>
       </c>
       <c r="C37">
-        <v>0.76</v>
+        <v>0.754</v>
       </c>
       <c r="D37">
-        <v>0.872</v>
+        <v>0.868</v>
       </c>
       <c r="E37">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="F37">
-        <v>32.976</v>
+        <v>33.792</v>
       </c>
       <c r="G37">
-        <v>36.393</v>
+        <v>37.195</v>
       </c>
       <c r="H37">
-        <v>32.837</v>
+        <v>33.736</v>
       </c>
       <c r="I37">
-        <v>36.313</v>
+        <v>37.139</v>
       </c>
       <c r="J37">
-        <v>33.075</v>
+        <v>33.863</v>
       </c>
       <c r="K37">
-        <v>36.551</v>
+        <v>37.266</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -1861,34 +1861,34 @@
         <v>13</v>
       </c>
       <c r="B38">
-        <v>29.274</v>
+        <v>30.006</v>
       </c>
       <c r="C38">
-        <v>0.58</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="D38">
-        <v>0.762</v>
+        <v>0.752</v>
       </c>
       <c r="E38">
         <v>0.024</v>
       </c>
       <c r="F38">
-        <v>27.883</v>
+        <v>28.625</v>
       </c>
       <c r="G38">
-        <v>30.868</v>
+        <v>31.573</v>
       </c>
       <c r="H38">
-        <v>27.834</v>
+        <v>28.568</v>
       </c>
       <c r="I38">
-        <v>30.901</v>
+        <v>31.617</v>
       </c>
       <c r="J38">
-        <v>27.748</v>
+        <v>28.488</v>
       </c>
       <c r="K38">
-        <v>30.815</v>
+        <v>31.537</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -1901,34 +1901,34 @@
         <v>14</v>
       </c>
       <c r="B39">
-        <v>29.973</v>
+        <v>30.641</v>
       </c>
       <c r="C39">
-        <v>0.671</v>
+        <v>0.627</v>
       </c>
       <c r="D39">
-        <v>0.819</v>
+        <v>0.792</v>
       </c>
       <c r="E39">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
       <c r="F39">
-        <v>28.469</v>
+        <v>29.189</v>
       </c>
       <c r="G39">
-        <v>31.68</v>
+        <v>32.292</v>
       </c>
       <c r="H39">
-        <v>28.306</v>
+        <v>29.085</v>
       </c>
       <c r="I39">
-        <v>31.65</v>
+        <v>32.252</v>
       </c>
       <c r="J39">
-        <v>28.397</v>
+        <v>29.129</v>
       </c>
       <c r="K39">
-        <v>31.741</v>
+        <v>32.296</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -1941,34 +1941,34 @@
         <v>15</v>
       </c>
       <c r="B40">
-        <v>27.976</v>
+        <v>28.701</v>
       </c>
       <c r="C40">
-        <v>0.583</v>
+        <v>0.595</v>
       </c>
       <c r="D40">
-        <v>0.764</v>
+        <v>0.772</v>
       </c>
       <c r="E40">
         <v>0.024</v>
       </c>
       <c r="F40">
-        <v>26.491</v>
+        <v>27.198</v>
       </c>
       <c r="G40">
-        <v>29.485</v>
+        <v>30.223</v>
       </c>
       <c r="H40">
-        <v>26.407</v>
+        <v>27.122</v>
       </c>
       <c r="I40">
-        <v>29.457</v>
+        <v>30.203</v>
       </c>
       <c r="J40">
-        <v>26.507</v>
+        <v>27.208</v>
       </c>
       <c r="K40">
-        <v>29.557</v>
+        <v>30.289</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -1981,34 +1981,34 @@
         <v>16</v>
       </c>
       <c r="B41">
-        <v>27.536</v>
+        <v>28.285</v>
       </c>
       <c r="C41">
-        <v>0.596</v>
+        <v>0.595</v>
       </c>
       <c r="D41">
-        <v>0.772</v>
+        <v>0.771</v>
       </c>
       <c r="E41">
         <v>0.024</v>
       </c>
       <c r="F41">
-        <v>25.97</v>
+        <v>26.72</v>
       </c>
       <c r="G41">
-        <v>28.995</v>
+        <v>29.743</v>
       </c>
       <c r="H41">
-        <v>25.932</v>
+        <v>26.699</v>
       </c>
       <c r="I41">
-        <v>28.935</v>
+        <v>29.676</v>
       </c>
       <c r="J41">
-        <v>26.084</v>
+        <v>26.841</v>
       </c>
       <c r="K41">
-        <v>29.087</v>
+        <v>29.818</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2021,34 +2021,34 @@
         <v>17</v>
       </c>
       <c r="B42">
-        <v>27.504</v>
+        <v>28.13</v>
       </c>
       <c r="C42">
-        <v>0.592</v>
+        <v>0.585</v>
       </c>
       <c r="D42">
-        <v>0.769</v>
+        <v>0.765</v>
       </c>
       <c r="E42">
         <v>0.024</v>
       </c>
       <c r="F42">
-        <v>26.043</v>
+        <v>26.673</v>
       </c>
       <c r="G42">
-        <v>29.059</v>
+        <v>29.671</v>
       </c>
       <c r="H42">
-        <v>26.072</v>
+        <v>26.715</v>
       </c>
       <c r="I42">
-        <v>29.013</v>
+        <v>29.612</v>
       </c>
       <c r="J42">
-        <v>26.042</v>
+        <v>26.69</v>
       </c>
       <c r="K42">
-        <v>28.983</v>
+        <v>29.587</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2061,34 +2061,34 @@
         <v>18</v>
       </c>
       <c r="B43">
-        <v>24.959</v>
+        <v>25.578</v>
       </c>
       <c r="C43">
-        <v>0.526</v>
+        <v>0.527</v>
       </c>
       <c r="D43">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="E43">
         <v>0.023</v>
       </c>
       <c r="F43">
-        <v>23.527</v>
+        <v>24.14</v>
       </c>
       <c r="G43">
-        <v>26.368</v>
+        <v>26.984</v>
       </c>
       <c r="H43">
-        <v>23.491</v>
+        <v>24.091</v>
       </c>
       <c r="I43">
-        <v>26.347</v>
+        <v>26.935</v>
       </c>
       <c r="J43">
-        <v>23.559</v>
+        <v>24.205</v>
       </c>
       <c r="K43">
-        <v>26.416</v>
+        <v>27.049</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2101,34 +2101,34 @@
         <v>19</v>
       </c>
       <c r="B44">
-        <v>24.834</v>
+        <v>25.204</v>
       </c>
       <c r="C44">
-        <v>1.448</v>
+        <v>0.964</v>
       </c>
       <c r="D44">
-        <v>1.203</v>
+        <v>0.982</v>
       </c>
       <c r="E44">
-        <v>0.038</v>
+        <v>0.031</v>
       </c>
       <c r="F44">
-        <v>22.562</v>
+        <v>23.345</v>
       </c>
       <c r="G44">
-        <v>27.279</v>
+        <v>27.194</v>
       </c>
       <c r="H44">
-        <v>22.28</v>
+        <v>23.176</v>
       </c>
       <c r="I44">
-        <v>26.944</v>
+        <v>27.031</v>
       </c>
       <c r="J44">
-        <v>22.811</v>
+        <v>23.443</v>
       </c>
       <c r="K44">
-        <v>27.474</v>
+        <v>27.297</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2141,34 +2141,34 @@
         <v>20</v>
       </c>
       <c r="B45">
-        <v>23.567</v>
+        <v>24.095</v>
       </c>
       <c r="C45">
-        <v>0.524</v>
+        <v>0.506</v>
       </c>
       <c r="D45">
-        <v>0.724</v>
+        <v>0.711</v>
       </c>
       <c r="E45">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="F45">
-        <v>22.119</v>
+        <v>22.676</v>
       </c>
       <c r="G45">
-        <v>24.957</v>
+        <v>25.464</v>
       </c>
       <c r="H45">
-        <v>22.115</v>
+        <v>22.67</v>
       </c>
       <c r="I45">
-        <v>24.881</v>
+        <v>25.418</v>
       </c>
       <c r="J45">
-        <v>22.224</v>
+        <v>22.747</v>
       </c>
       <c r="K45">
-        <v>24.99</v>
+        <v>25.495</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2181,34 +2181,34 @@
         <v>21</v>
       </c>
       <c r="B46">
-        <v>22.774</v>
+        <v>23.398</v>
       </c>
       <c r="C46">
-        <v>0.518</v>
+        <v>0.513</v>
       </c>
       <c r="D46">
-        <v>0.72</v>
+        <v>0.716</v>
       </c>
       <c r="E46">
         <v>0.023</v>
       </c>
       <c r="F46">
-        <v>21.331</v>
+        <v>21.965</v>
       </c>
       <c r="G46">
-        <v>24.153</v>
+        <v>24.773</v>
       </c>
       <c r="H46">
-        <v>21.282</v>
+        <v>21.929</v>
       </c>
       <c r="I46">
-        <v>24.085</v>
+        <v>24.718</v>
       </c>
       <c r="J46">
-        <v>21.431</v>
+        <v>22.05</v>
       </c>
       <c r="K46">
-        <v>24.234</v>
+        <v>24.839</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2221,34 +2221,34 @@
         <v>22</v>
       </c>
       <c r="B47">
-        <v>20.626</v>
+        <v>21.165</v>
       </c>
       <c r="C47">
-        <v>0.428</v>
+        <v>0.43</v>
       </c>
       <c r="D47">
-        <v>0.654</v>
+        <v>0.655</v>
       </c>
       <c r="E47">
         <v>0.021</v>
       </c>
       <c r="F47">
-        <v>19.404</v>
+        <v>19.941</v>
       </c>
       <c r="G47">
-        <v>21.968</v>
+        <v>22.511</v>
       </c>
       <c r="H47">
-        <v>19.473</v>
+        <v>20.01</v>
       </c>
       <c r="I47">
-        <v>21.935</v>
+        <v>22.48</v>
       </c>
       <c r="J47">
-        <v>19.377</v>
+        <v>19.911</v>
       </c>
       <c r="K47">
-        <v>21.84</v>
+        <v>22.381</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2261,34 +2261,34 @@
         <v>23</v>
       </c>
       <c r="B48">
-        <v>20.365</v>
+        <v>20.988</v>
       </c>
       <c r="C48">
-        <v>0.49</v>
+        <v>0.492</v>
       </c>
       <c r="D48">
-        <v>0.7</v>
+        <v>0.702</v>
       </c>
       <c r="E48">
         <v>0.022</v>
       </c>
       <c r="F48">
-        <v>18.945</v>
+        <v>19.564</v>
       </c>
       <c r="G48">
-        <v>21.69</v>
+        <v>22.314</v>
       </c>
       <c r="H48">
-        <v>18.941</v>
+        <v>19.55</v>
       </c>
       <c r="I48">
-        <v>21.656</v>
+        <v>22.224</v>
       </c>
       <c r="J48">
-        <v>19.027</v>
+        <v>19.703</v>
       </c>
       <c r="K48">
-        <v>21.742</v>
+        <v>22.377</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2301,34 +2301,34 @@
         <v>24</v>
       </c>
       <c r="B49">
-        <v>18.464</v>
+        <v>19.056</v>
       </c>
       <c r="C49">
-        <v>0.347</v>
+        <v>0.352</v>
       </c>
       <c r="D49">
-        <v>0.589</v>
+        <v>0.593</v>
       </c>
       <c r="E49">
         <v>0.019</v>
       </c>
       <c r="F49">
-        <v>17.281</v>
+        <v>17.867</v>
       </c>
       <c r="G49">
-        <v>19.589</v>
+        <v>20.192</v>
       </c>
       <c r="H49">
-        <v>17.16</v>
+        <v>17.708</v>
       </c>
       <c r="I49">
-        <v>19.585</v>
+        <v>20.165</v>
       </c>
       <c r="J49">
-        <v>17.314</v>
+        <v>17.92</v>
       </c>
       <c r="K49">
-        <v>19.739</v>
+        <v>20.377</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/monthly_bootstrap_combined_data_costs_users.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/monthly_bootstrap_combined_data_costs_users.xlsx
@@ -421,34 +421,34 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>271.688</v>
+        <v>274.236</v>
       </c>
       <c r="C2">
-        <v>6.249</v>
+        <v>6.982</v>
       </c>
       <c r="D2">
-        <v>2.5</v>
+        <v>2.642</v>
       </c>
       <c r="E2">
-        <v>0.079</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F2">
-        <v>266.884</v>
+        <v>269.113</v>
       </c>
       <c r="G2">
-        <v>276.683</v>
+        <v>279.47</v>
       </c>
       <c r="H2">
-        <v>266.827</v>
+        <v>269.102</v>
       </c>
       <c r="I2">
-        <v>276.449</v>
+        <v>279.38</v>
       </c>
       <c r="J2">
-        <v>267.022</v>
+        <v>269.147</v>
       </c>
       <c r="K2">
-        <v>276.644</v>
+        <v>279.426</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -461,34 +461,34 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>182.813</v>
+        <v>184.595</v>
       </c>
       <c r="C3">
-        <v>3.953</v>
+        <v>4.237</v>
       </c>
       <c r="D3">
-        <v>1.988</v>
+        <v>2.058</v>
       </c>
       <c r="E3">
-        <v>0.063</v>
+        <v>0.065</v>
       </c>
       <c r="F3">
-        <v>178.942</v>
+        <v>180.594</v>
       </c>
       <c r="G3">
-        <v>186.737</v>
+        <v>188.663</v>
       </c>
       <c r="H3">
-        <v>178.639</v>
+        <v>180.308</v>
       </c>
       <c r="I3">
-        <v>186.64</v>
+        <v>188.566</v>
       </c>
       <c r="J3">
-        <v>179.013</v>
+        <v>180.657</v>
       </c>
       <c r="K3">
-        <v>187.013</v>
+        <v>188.915</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -501,34 +501,34 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>121.591</v>
+        <v>123.027</v>
       </c>
       <c r="C4">
-        <v>2.545</v>
+        <v>2.885</v>
       </c>
       <c r="D4">
-        <v>1.595</v>
+        <v>1.699</v>
       </c>
       <c r="E4">
-        <v>0.05</v>
+        <v>0.054</v>
       </c>
       <c r="F4">
-        <v>118.501</v>
+        <v>119.766</v>
       </c>
       <c r="G4">
-        <v>124.756</v>
+        <v>126.425</v>
       </c>
       <c r="H4">
-        <v>118.337</v>
+        <v>119.354</v>
       </c>
       <c r="I4">
-        <v>124.657</v>
+        <v>126.323</v>
       </c>
       <c r="J4">
-        <v>118.562</v>
+        <v>119.8</v>
       </c>
       <c r="K4">
-        <v>124.882</v>
+        <v>126.768</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -541,34 +541,34 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>86.646</v>
+        <v>87.504</v>
       </c>
       <c r="C5">
-        <v>3.227</v>
+        <v>3.291</v>
       </c>
       <c r="D5">
-        <v>1.796</v>
+        <v>1.814</v>
       </c>
       <c r="E5">
         <v>0.057</v>
       </c>
       <c r="F5">
-        <v>83.14100000000001</v>
+        <v>83.974</v>
       </c>
       <c r="G5">
-        <v>90.182</v>
+        <v>91.08499999999999</v>
       </c>
       <c r="H5">
-        <v>82.693</v>
+        <v>83.506</v>
       </c>
       <c r="I5">
-        <v>89.92400000000001</v>
+        <v>90.822</v>
       </c>
       <c r="J5">
-        <v>83.383</v>
+        <v>84.211</v>
       </c>
       <c r="K5">
-        <v>90.614</v>
+        <v>91.527</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -581,34 +581,34 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>66.613</v>
+        <v>67.52</v>
       </c>
       <c r="C6">
-        <v>1.296</v>
+        <v>1.344</v>
       </c>
       <c r="D6">
-        <v>1.138</v>
+        <v>1.159</v>
       </c>
       <c r="E6">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
       <c r="F6">
-        <v>64.44199999999999</v>
+        <v>65.3</v>
       </c>
       <c r="G6">
-        <v>68.904</v>
+        <v>69.84399999999999</v>
       </c>
       <c r="H6">
-        <v>64.3</v>
+        <v>65.205</v>
       </c>
       <c r="I6">
-        <v>68.89100000000001</v>
+        <v>69.873</v>
       </c>
       <c r="J6">
-        <v>64.39400000000001</v>
+        <v>65.21899999999999</v>
       </c>
       <c r="K6">
-        <v>68.985</v>
+        <v>69.887</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -621,34 +621,34 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>54.278</v>
+        <v>55.079</v>
       </c>
       <c r="C7">
-        <v>1.103</v>
+        <v>1.146</v>
       </c>
       <c r="D7">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="E7">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="F7">
-        <v>52.181</v>
+        <v>52.938</v>
       </c>
       <c r="G7">
-        <v>56.298</v>
+        <v>57.135</v>
       </c>
       <c r="H7">
-        <v>52.134</v>
+        <v>52.913</v>
       </c>
       <c r="I7">
-        <v>56.243</v>
+        <v>57.052</v>
       </c>
       <c r="J7">
-        <v>52.274</v>
+        <v>53.063</v>
       </c>
       <c r="K7">
-        <v>56.383</v>
+        <v>57.202</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -661,34 +661,34 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>46.702</v>
+        <v>47.727</v>
       </c>
       <c r="C8">
-        <v>0.997</v>
+        <v>1.16</v>
       </c>
       <c r="D8">
-        <v>0.999</v>
+        <v>1.077</v>
       </c>
       <c r="E8">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="F8">
-        <v>44.762</v>
+        <v>45.611</v>
       </c>
       <c r="G8">
-        <v>48.676</v>
+        <v>49.832</v>
       </c>
       <c r="H8">
-        <v>44.758</v>
+        <v>45.522</v>
       </c>
       <c r="I8">
-        <v>48.691</v>
+        <v>49.878</v>
       </c>
       <c r="J8">
-        <v>44.73</v>
+        <v>45.57</v>
       </c>
       <c r="K8">
-        <v>48.663</v>
+        <v>49.926</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -701,34 +701,34 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>40.493</v>
+        <v>41.435</v>
       </c>
       <c r="C9">
-        <v>0.824</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="D9">
-        <v>0.908</v>
+        <v>0.967</v>
       </c>
       <c r="E9">
-        <v>0.029</v>
+        <v>0.031</v>
       </c>
       <c r="F9">
-        <v>38.641</v>
+        <v>39.464</v>
       </c>
       <c r="G9">
-        <v>42.199</v>
+        <v>43.256</v>
       </c>
       <c r="H9">
-        <v>38.646</v>
+        <v>39.498</v>
       </c>
       <c r="I9">
-        <v>42.202</v>
+        <v>43.333</v>
       </c>
       <c r="J9">
-        <v>38.71</v>
+        <v>39.463</v>
       </c>
       <c r="K9">
-        <v>42.267</v>
+        <v>43.298</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -741,34 +741,34 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>36.168</v>
+        <v>36.966</v>
       </c>
       <c r="C10">
-        <v>0.65</v>
+        <v>0.713</v>
       </c>
       <c r="D10">
-        <v>0.806</v>
+        <v>0.844</v>
       </c>
       <c r="E10">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="F10">
-        <v>34.518</v>
+        <v>35.245</v>
       </c>
       <c r="G10">
-        <v>37.678</v>
+        <v>38.555</v>
       </c>
       <c r="H10">
-        <v>34.458</v>
+        <v>35.258</v>
       </c>
       <c r="I10">
-        <v>37.656</v>
+        <v>38.573</v>
       </c>
       <c r="J10">
-        <v>34.609</v>
+        <v>35.292</v>
       </c>
       <c r="K10">
-        <v>37.808</v>
+        <v>38.607</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -781,34 +781,34 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>34.853</v>
+        <v>35.628</v>
       </c>
       <c r="C11">
-        <v>0.631</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="D11">
-        <v>0.794</v>
+        <v>0.829</v>
       </c>
       <c r="E11">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="F11">
-        <v>33.252</v>
+        <v>33.965</v>
       </c>
       <c r="G11">
-        <v>36.365</v>
+        <v>37.215</v>
       </c>
       <c r="H11">
-        <v>33.184</v>
+        <v>33.881</v>
       </c>
       <c r="I11">
-        <v>36.451</v>
+        <v>37.246</v>
       </c>
       <c r="J11">
-        <v>33.211</v>
+        <v>33.972</v>
       </c>
       <c r="K11">
-        <v>36.477</v>
+        <v>37.336</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -821,34 +821,34 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>32.405</v>
+        <v>33.254</v>
       </c>
       <c r="C12">
-        <v>0.671</v>
+        <v>0.721</v>
       </c>
       <c r="D12">
-        <v>0.819</v>
+        <v>0.849</v>
       </c>
       <c r="E12">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="F12">
-        <v>30.861</v>
+        <v>31.657</v>
       </c>
       <c r="G12">
-        <v>34.072</v>
+        <v>34.986</v>
       </c>
       <c r="H12">
-        <v>30.815</v>
+        <v>31.611</v>
       </c>
       <c r="I12">
-        <v>34.001</v>
+        <v>34.92</v>
       </c>
       <c r="J12">
-        <v>30.871</v>
+        <v>31.656</v>
       </c>
       <c r="K12">
-        <v>34.057</v>
+        <v>34.964</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -861,34 +861,34 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>33.327</v>
+        <v>34.096</v>
       </c>
       <c r="C13">
-        <v>0.605</v>
+        <v>0.656</v>
       </c>
       <c r="D13">
-        <v>0.778</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E13">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="F13">
-        <v>31.809</v>
+        <v>32.526</v>
       </c>
       <c r="G13">
-        <v>34.857</v>
+        <v>35.701</v>
       </c>
       <c r="H13">
-        <v>31.752</v>
+        <v>32.479</v>
       </c>
       <c r="I13">
-        <v>34.8</v>
+        <v>35.64</v>
       </c>
       <c r="J13">
-        <v>31.86</v>
+        <v>32.57</v>
       </c>
       <c r="K13">
-        <v>34.908</v>
+        <v>35.731</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -901,34 +901,34 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>28.569</v>
+        <v>29.246</v>
       </c>
       <c r="C14">
-        <v>0.48</v>
+        <v>0.535</v>
       </c>
       <c r="D14">
-        <v>0.6929999999999999</v>
+        <v>0.732</v>
       </c>
       <c r="E14">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="F14">
-        <v>27.153</v>
+        <v>27.77</v>
       </c>
       <c r="G14">
-        <v>29.869</v>
+        <v>30.638</v>
       </c>
       <c r="H14">
-        <v>27.063</v>
+        <v>27.681</v>
       </c>
       <c r="I14">
-        <v>29.858</v>
+        <v>30.641</v>
       </c>
       <c r="J14">
-        <v>27.222</v>
+        <v>27.81</v>
       </c>
       <c r="K14">
-        <v>30.017</v>
+        <v>30.769</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -941,34 +941,34 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>28.708</v>
+        <v>29.39</v>
       </c>
       <c r="C15">
-        <v>0.47</v>
+        <v>0.535</v>
       </c>
       <c r="D15">
-        <v>0.6850000000000001</v>
+        <v>0.732</v>
       </c>
       <c r="E15">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="F15">
-        <v>27.349</v>
+        <v>27.918</v>
       </c>
       <c r="G15">
-        <v>30.036</v>
+        <v>30.786</v>
       </c>
       <c r="H15">
-        <v>27.31</v>
+        <v>27.819</v>
       </c>
       <c r="I15">
-        <v>30.059</v>
+        <v>30.805</v>
       </c>
       <c r="J15">
-        <v>27.341</v>
+        <v>27.936</v>
       </c>
       <c r="K15">
-        <v>30.091</v>
+        <v>30.922</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -981,34 +981,34 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>26.801</v>
+        <v>27.527</v>
       </c>
       <c r="C16">
-        <v>0.519</v>
+        <v>0.576</v>
       </c>
       <c r="D16">
-        <v>0.721</v>
+        <v>0.759</v>
       </c>
       <c r="E16">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="F16">
-        <v>25.393</v>
+        <v>26.028</v>
       </c>
       <c r="G16">
-        <v>28.217</v>
+        <v>29.003</v>
       </c>
       <c r="H16">
-        <v>25.301</v>
+        <v>26.033</v>
       </c>
       <c r="I16">
-        <v>28.134</v>
+        <v>28.927</v>
       </c>
       <c r="J16">
-        <v>25.472</v>
+        <v>26.115</v>
       </c>
       <c r="K16">
-        <v>28.306</v>
+        <v>29.01</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1021,34 +1021,34 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>26.552</v>
+        <v>27.049</v>
       </c>
       <c r="C17">
-        <v>0.52</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="D17">
-        <v>0.721</v>
+        <v>0.754</v>
       </c>
       <c r="E17">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="F17">
-        <v>25.117</v>
+        <v>25.556</v>
       </c>
       <c r="G17">
-        <v>27.945</v>
+        <v>28.511</v>
       </c>
       <c r="H17">
-        <v>25.096</v>
+        <v>25.563</v>
       </c>
       <c r="I17">
-        <v>27.94</v>
+        <v>28.438</v>
       </c>
       <c r="J17">
-        <v>25.143</v>
+        <v>25.645</v>
       </c>
       <c r="K17">
-        <v>27.987</v>
+        <v>28.52</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1061,34 +1061,34 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>26.14</v>
+        <v>26.811</v>
       </c>
       <c r="C18">
-        <v>0.527</v>
+        <v>0.577</v>
       </c>
       <c r="D18">
-        <v>0.726</v>
+        <v>0.759</v>
       </c>
       <c r="E18">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="F18">
-        <v>24.687</v>
+        <v>25.298</v>
       </c>
       <c r="G18">
-        <v>27.531</v>
+        <v>28.275</v>
       </c>
       <c r="H18">
-        <v>24.647</v>
+        <v>25.248</v>
       </c>
       <c r="I18">
-        <v>27.527</v>
+        <v>28.227</v>
       </c>
       <c r="J18">
-        <v>24.722</v>
+        <v>25.371</v>
       </c>
       <c r="K18">
-        <v>27.602</v>
+        <v>28.35</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1101,34 +1101,34 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>24.068</v>
+        <v>24.561</v>
       </c>
       <c r="C19">
-        <v>0.467</v>
+        <v>0.501</v>
       </c>
       <c r="D19">
-        <v>0.6830000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="E19">
         <v>0.022</v>
       </c>
       <c r="F19">
-        <v>22.771</v>
+        <v>23.227</v>
       </c>
       <c r="G19">
-        <v>25.45</v>
+        <v>26.001</v>
       </c>
       <c r="H19">
-        <v>22.69</v>
+        <v>23.128</v>
       </c>
       <c r="I19">
-        <v>25.392</v>
+        <v>25.96</v>
       </c>
       <c r="J19">
-        <v>22.787</v>
+        <v>23.215</v>
       </c>
       <c r="K19">
-        <v>25.488</v>
+        <v>26.047</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1141,34 +1141,34 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>23.23</v>
+        <v>24.162</v>
       </c>
       <c r="C20">
-        <v>0.486</v>
+        <v>0.978</v>
       </c>
       <c r="D20">
-        <v>0.697</v>
+        <v>0.989</v>
       </c>
       <c r="E20">
-        <v>0.022</v>
+        <v>0.031</v>
       </c>
       <c r="F20">
-        <v>21.866</v>
+        <v>22.278</v>
       </c>
       <c r="G20">
-        <v>24.6</v>
+        <v>26.155</v>
       </c>
       <c r="H20">
-        <v>21.825</v>
+        <v>21.913</v>
       </c>
       <c r="I20">
-        <v>24.534</v>
+        <v>25.914</v>
       </c>
       <c r="J20">
-        <v>21.929</v>
+        <v>22.465</v>
       </c>
       <c r="K20">
-        <v>24.637</v>
+        <v>26.465</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1181,34 +1181,34 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>22.637</v>
+        <v>23.186</v>
       </c>
       <c r="C21">
-        <v>0.436</v>
+        <v>0.488</v>
       </c>
       <c r="D21">
-        <v>0.66</v>
+        <v>0.699</v>
       </c>
       <c r="E21">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="F21">
-        <v>21.297</v>
+        <v>21.765</v>
       </c>
       <c r="G21">
-        <v>23.886</v>
+        <v>24.504</v>
       </c>
       <c r="H21">
-        <v>21.185</v>
+        <v>21.715</v>
       </c>
       <c r="I21">
-        <v>23.857</v>
+        <v>24.451</v>
       </c>
       <c r="J21">
-        <v>21.371</v>
+        <v>21.869</v>
       </c>
       <c r="K21">
-        <v>24.043</v>
+        <v>24.605</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>21.837</v>
+        <v>22.221</v>
       </c>
       <c r="C22">
-        <v>0.474</v>
+        <v>0.504</v>
       </c>
       <c r="D22">
-        <v>0.6879999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="E22">
         <v>0.022</v>
       </c>
       <c r="F22">
-        <v>20.474</v>
+        <v>20.806</v>
       </c>
       <c r="G22">
-        <v>23.172</v>
+        <v>23.589</v>
       </c>
       <c r="H22">
-        <v>20.386</v>
+        <v>20.733</v>
       </c>
       <c r="I22">
-        <v>23.149</v>
+        <v>23.552</v>
       </c>
       <c r="J22">
-        <v>20.511</v>
+        <v>20.867</v>
       </c>
       <c r="K22">
-        <v>23.274</v>
+        <v>23.685</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1261,34 +1261,34 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>20.043</v>
+        <v>20.437</v>
       </c>
       <c r="C23">
-        <v>0.373</v>
+        <v>0.39</v>
       </c>
       <c r="D23">
-        <v>0.61</v>
+        <v>0.624</v>
       </c>
       <c r="E23">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="F23">
-        <v>18.86</v>
+        <v>19.229</v>
       </c>
       <c r="G23">
-        <v>21.253</v>
+        <v>21.675</v>
       </c>
       <c r="H23">
-        <v>18.808</v>
+        <v>19.188</v>
       </c>
       <c r="I23">
-        <v>21.233</v>
+        <v>21.673</v>
       </c>
       <c r="J23">
-        <v>18.866</v>
+        <v>19.217</v>
       </c>
       <c r="K23">
-        <v>21.291</v>
+        <v>21.701</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1301,34 +1301,34 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>19.88</v>
+        <v>20.105</v>
       </c>
       <c r="C24">
-        <v>0.436</v>
+        <v>0.441</v>
       </c>
       <c r="D24">
-        <v>0.66</v>
+        <v>0.664</v>
       </c>
       <c r="E24">
         <v>0.021</v>
       </c>
       <c r="F24">
-        <v>18.537</v>
+        <v>18.752</v>
       </c>
       <c r="G24">
-        <v>21.124</v>
+        <v>21.355</v>
       </c>
       <c r="H24">
-        <v>18.573</v>
+        <v>18.755</v>
       </c>
       <c r="I24">
-        <v>21.165</v>
+        <v>21.365</v>
       </c>
       <c r="J24">
-        <v>18.545</v>
+        <v>18.793</v>
       </c>
       <c r="K24">
-        <v>21.138</v>
+        <v>21.403</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1341,34 +1341,34 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>18.081</v>
+        <v>18.376</v>
       </c>
       <c r="C25">
-        <v>0.332</v>
+        <v>0.351</v>
       </c>
       <c r="D25">
-        <v>0.576</v>
+        <v>0.593</v>
       </c>
       <c r="E25">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="F25">
-        <v>16.945</v>
+        <v>17.205</v>
       </c>
       <c r="G25">
-        <v>19.203</v>
+        <v>19.529</v>
       </c>
       <c r="H25">
-        <v>16.993</v>
+        <v>17.228</v>
       </c>
       <c r="I25">
-        <v>19.174</v>
+        <v>19.499</v>
       </c>
       <c r="J25">
-        <v>16.98</v>
+        <v>17.244</v>
       </c>
       <c r="K25">
-        <v>19.161</v>
+        <v>19.514</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/monthly_bootstrap_combined_data_costs_users.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/monthly_bootstrap_combined_data_costs_users.xlsx
@@ -421,34 +421,34 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>274.236</v>
+        <v>257.074</v>
       </c>
       <c r="C2">
-        <v>6.982</v>
+        <v>5.839</v>
       </c>
       <c r="D2">
-        <v>2.642</v>
+        <v>2.416</v>
       </c>
       <c r="E2">
-        <v>0.08400000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="F2">
-        <v>269.113</v>
+        <v>252.456</v>
       </c>
       <c r="G2">
-        <v>279.47</v>
+        <v>261.928</v>
       </c>
       <c r="H2">
-        <v>269.102</v>
+        <v>252.289</v>
       </c>
       <c r="I2">
-        <v>279.38</v>
+        <v>261.758</v>
       </c>
       <c r="J2">
-        <v>269.147</v>
+        <v>252.508</v>
       </c>
       <c r="K2">
-        <v>279.426</v>
+        <v>261.977</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -461,34 +461,34 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>184.595</v>
+        <v>182.884</v>
       </c>
       <c r="C3">
-        <v>4.237</v>
+        <v>3.958</v>
       </c>
       <c r="D3">
-        <v>2.058</v>
+        <v>1.989</v>
       </c>
       <c r="E3">
-        <v>0.065</v>
+        <v>0.063</v>
       </c>
       <c r="F3">
-        <v>180.594</v>
+        <v>179.008</v>
       </c>
       <c r="G3">
-        <v>188.663</v>
+        <v>186.807</v>
       </c>
       <c r="H3">
-        <v>180.308</v>
+        <v>178.862</v>
       </c>
       <c r="I3">
-        <v>188.566</v>
+        <v>186.655</v>
       </c>
       <c r="J3">
-        <v>180.657</v>
+        <v>179.136</v>
       </c>
       <c r="K3">
-        <v>188.915</v>
+        <v>186.929</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -501,34 +501,34 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>123.027</v>
+        <v>126.795</v>
       </c>
       <c r="C4">
-        <v>2.885</v>
+        <v>2.631</v>
       </c>
       <c r="D4">
-        <v>1.699</v>
+        <v>1.622</v>
       </c>
       <c r="E4">
-        <v>0.054</v>
+        <v>0.051</v>
       </c>
       <c r="F4">
-        <v>119.766</v>
+        <v>123.661</v>
       </c>
       <c r="G4">
-        <v>126.425</v>
+        <v>130.019</v>
       </c>
       <c r="H4">
-        <v>119.354</v>
+        <v>123.529</v>
       </c>
       <c r="I4">
-        <v>126.323</v>
+        <v>129.943</v>
       </c>
       <c r="J4">
-        <v>119.8</v>
+        <v>123.692</v>
       </c>
       <c r="K4">
-        <v>126.768</v>
+        <v>130.107</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -541,34 +541,34 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>87.504</v>
+        <v>90.12</v>
       </c>
       <c r="C5">
-        <v>3.291</v>
+        <v>3.175</v>
       </c>
       <c r="D5">
-        <v>1.814</v>
+        <v>1.782</v>
       </c>
       <c r="E5">
-        <v>0.057</v>
+        <v>0.056</v>
       </c>
       <c r="F5">
-        <v>83.974</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="G5">
-        <v>91.08499999999999</v>
+        <v>93.666</v>
       </c>
       <c r="H5">
-        <v>83.506</v>
+        <v>86.289</v>
       </c>
       <c r="I5">
-        <v>90.822</v>
+        <v>93.38800000000001</v>
       </c>
       <c r="J5">
-        <v>84.211</v>
+        <v>86.90600000000001</v>
       </c>
       <c r="K5">
-        <v>91.527</v>
+        <v>94.005</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -581,34 +581,34 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>67.52</v>
+        <v>69.002</v>
       </c>
       <c r="C6">
-        <v>1.344</v>
+        <v>1.329</v>
       </c>
       <c r="D6">
-        <v>1.159</v>
+        <v>1.153</v>
       </c>
       <c r="E6">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="F6">
-        <v>65.3</v>
+        <v>66.798</v>
       </c>
       <c r="G6">
-        <v>69.84399999999999</v>
+        <v>71.31699999999999</v>
       </c>
       <c r="H6">
-        <v>65.205</v>
+        <v>66.703</v>
       </c>
       <c r="I6">
-        <v>69.873</v>
+        <v>71.247</v>
       </c>
       <c r="J6">
-        <v>65.21899999999999</v>
+        <v>66.812</v>
       </c>
       <c r="K6">
-        <v>69.887</v>
+        <v>71.35599999999999</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -621,34 +621,34 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>55.079</v>
+        <v>55.284</v>
       </c>
       <c r="C7">
-        <v>1.146</v>
+        <v>1.065</v>
       </c>
       <c r="D7">
-        <v>1.07</v>
+        <v>1.032</v>
       </c>
       <c r="E7">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="F7">
-        <v>52.938</v>
+        <v>53.209</v>
       </c>
       <c r="G7">
-        <v>57.135</v>
+        <v>57.254</v>
       </c>
       <c r="H7">
-        <v>52.913</v>
+        <v>53.149</v>
       </c>
       <c r="I7">
-        <v>57.052</v>
+        <v>57.223</v>
       </c>
       <c r="J7">
-        <v>53.063</v>
+        <v>53.292</v>
       </c>
       <c r="K7">
-        <v>57.202</v>
+        <v>57.366</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -661,34 +661,34 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>47.727</v>
+        <v>46.587</v>
       </c>
       <c r="C8">
-        <v>1.16</v>
+        <v>0.907</v>
       </c>
       <c r="D8">
-        <v>1.077</v>
+        <v>0.952</v>
       </c>
       <c r="E8">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="F8">
-        <v>45.611</v>
+        <v>44.732</v>
       </c>
       <c r="G8">
-        <v>49.832</v>
+        <v>48.466</v>
       </c>
       <c r="H8">
-        <v>45.522</v>
+        <v>44.667</v>
       </c>
       <c r="I8">
-        <v>49.878</v>
+        <v>48.457</v>
       </c>
       <c r="J8">
-        <v>45.57</v>
+        <v>44.729</v>
       </c>
       <c r="K8">
-        <v>49.926</v>
+        <v>48.518</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -701,34 +701,34 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>41.435</v>
+        <v>40.314</v>
       </c>
       <c r="C9">
-        <v>0.9360000000000001</v>
+        <v>0.759</v>
       </c>
       <c r="D9">
-        <v>0.967</v>
+        <v>0.871</v>
       </c>
       <c r="E9">
-        <v>0.031</v>
+        <v>0.028</v>
       </c>
       <c r="F9">
-        <v>39.464</v>
+        <v>38.532</v>
       </c>
       <c r="G9">
-        <v>43.256</v>
+        <v>41.948</v>
       </c>
       <c r="H9">
-        <v>39.498</v>
+        <v>38.577</v>
       </c>
       <c r="I9">
-        <v>43.333</v>
+        <v>42.03</v>
       </c>
       <c r="J9">
-        <v>39.463</v>
+        <v>38.525</v>
       </c>
       <c r="K9">
-        <v>43.298</v>
+        <v>41.977</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -741,34 +741,34 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>36.966</v>
+        <v>35.655</v>
       </c>
       <c r="C10">
-        <v>0.713</v>
+        <v>0.586</v>
       </c>
       <c r="D10">
-        <v>0.844</v>
+        <v>0.765</v>
       </c>
       <c r="E10">
-        <v>0.027</v>
+        <v>0.024</v>
       </c>
       <c r="F10">
-        <v>35.245</v>
+        <v>34.077</v>
       </c>
       <c r="G10">
-        <v>38.555</v>
+        <v>37.077</v>
       </c>
       <c r="H10">
-        <v>35.258</v>
+        <v>34.023</v>
       </c>
       <c r="I10">
-        <v>38.573</v>
+        <v>37.077</v>
       </c>
       <c r="J10">
-        <v>35.292</v>
+        <v>34.156</v>
       </c>
       <c r="K10">
-        <v>38.607</v>
+        <v>37.21</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -781,34 +781,34 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>35.628</v>
+        <v>34.306</v>
       </c>
       <c r="C11">
-        <v>0.6879999999999999</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="D11">
-        <v>0.829</v>
+        <v>0.753</v>
       </c>
       <c r="E11">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="F11">
-        <v>33.965</v>
+        <v>32.789</v>
       </c>
       <c r="G11">
-        <v>37.215</v>
+        <v>35.742</v>
       </c>
       <c r="H11">
-        <v>33.881</v>
+        <v>32.705</v>
       </c>
       <c r="I11">
-        <v>37.246</v>
+        <v>35.782</v>
       </c>
       <c r="J11">
-        <v>33.972</v>
+        <v>32.79</v>
       </c>
       <c r="K11">
-        <v>37.336</v>
+        <v>35.867</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -821,34 +821,34 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>33.254</v>
+        <v>31.949</v>
       </c>
       <c r="C12">
-        <v>0.721</v>
+        <v>0.644</v>
       </c>
       <c r="D12">
-        <v>0.849</v>
+        <v>0.802</v>
       </c>
       <c r="E12">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
       <c r="F12">
-        <v>31.657</v>
+        <v>30.439</v>
       </c>
       <c r="G12">
-        <v>34.986</v>
+        <v>33.583</v>
       </c>
       <c r="H12">
-        <v>31.611</v>
+        <v>30.442</v>
       </c>
       <c r="I12">
-        <v>34.92</v>
+        <v>33.447</v>
       </c>
       <c r="J12">
-        <v>31.656</v>
+        <v>30.513</v>
       </c>
       <c r="K12">
-        <v>34.964</v>
+        <v>33.518</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -861,34 +861,34 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>34.096</v>
+        <v>32.762</v>
       </c>
       <c r="C13">
-        <v>0.656</v>
+        <v>0.569</v>
       </c>
       <c r="D13">
-        <v>0.8100000000000001</v>
+        <v>0.754</v>
       </c>
       <c r="E13">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="F13">
-        <v>32.526</v>
+        <v>31.295</v>
       </c>
       <c r="G13">
-        <v>35.701</v>
+        <v>34.252</v>
       </c>
       <c r="H13">
-        <v>32.479</v>
+        <v>31.313</v>
       </c>
       <c r="I13">
-        <v>35.64</v>
+        <v>34.205</v>
       </c>
       <c r="J13">
-        <v>32.57</v>
+        <v>31.33</v>
       </c>
       <c r="K13">
-        <v>35.731</v>
+        <v>34.222</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -901,34 +901,34 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>29.246</v>
+        <v>28.061</v>
       </c>
       <c r="C14">
-        <v>0.535</v>
+        <v>0.446</v>
       </c>
       <c r="D14">
-        <v>0.732</v>
+        <v>0.668</v>
       </c>
       <c r="E14">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="F14">
-        <v>27.77</v>
+        <v>26.704</v>
       </c>
       <c r="G14">
-        <v>30.638</v>
+        <v>29.323</v>
       </c>
       <c r="H14">
-        <v>27.681</v>
+        <v>26.648</v>
       </c>
       <c r="I14">
-        <v>30.641</v>
+        <v>29.319</v>
       </c>
       <c r="J14">
-        <v>27.81</v>
+        <v>26.755</v>
       </c>
       <c r="K14">
-        <v>30.769</v>
+        <v>29.426</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -941,34 +941,34 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>29.39</v>
+        <v>28.06</v>
       </c>
       <c r="C15">
-        <v>0.535</v>
+        <v>0.439</v>
       </c>
       <c r="D15">
-        <v>0.732</v>
+        <v>0.663</v>
       </c>
       <c r="E15">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="F15">
-        <v>27.918</v>
+        <v>26.738</v>
       </c>
       <c r="G15">
-        <v>30.786</v>
+        <v>29.336</v>
       </c>
       <c r="H15">
-        <v>27.819</v>
+        <v>26.755</v>
       </c>
       <c r="I15">
-        <v>30.805</v>
+        <v>29.343</v>
       </c>
       <c r="J15">
-        <v>27.936</v>
+        <v>26.754</v>
       </c>
       <c r="K15">
-        <v>30.922</v>
+        <v>29.342</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -981,34 +981,34 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>27.527</v>
+        <v>26.325</v>
       </c>
       <c r="C16">
-        <v>0.576</v>
+        <v>0.445</v>
       </c>
       <c r="D16">
-        <v>0.759</v>
+        <v>0.667</v>
       </c>
       <c r="E16">
-        <v>0.024</v>
+        <v>0.021</v>
       </c>
       <c r="F16">
-        <v>26.028</v>
+        <v>25.023</v>
       </c>
       <c r="G16">
-        <v>29.003</v>
+        <v>27.638</v>
       </c>
       <c r="H16">
-        <v>26.033</v>
+        <v>24.964</v>
       </c>
       <c r="I16">
-        <v>28.927</v>
+        <v>27.586</v>
       </c>
       <c r="J16">
-        <v>26.115</v>
+        <v>25.07</v>
       </c>
       <c r="K16">
-        <v>29.01</v>
+        <v>27.691</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1021,34 +1021,34 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>27.049</v>
+        <v>26.472</v>
       </c>
       <c r="C17">
-        <v>0.5679999999999999</v>
+        <v>0.552</v>
       </c>
       <c r="D17">
-        <v>0.754</v>
+        <v>0.743</v>
       </c>
       <c r="E17">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="F17">
-        <v>25.556</v>
+        <v>24.986</v>
       </c>
       <c r="G17">
-        <v>28.511</v>
+        <v>27.899</v>
       </c>
       <c r="H17">
-        <v>25.563</v>
+        <v>24.974</v>
       </c>
       <c r="I17">
-        <v>28.438</v>
+        <v>27.802</v>
       </c>
       <c r="J17">
-        <v>25.645</v>
+        <v>25.113</v>
       </c>
       <c r="K17">
-        <v>28.52</v>
+        <v>27.94</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1061,34 +1061,34 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>26.811</v>
+        <v>25.621</v>
       </c>
       <c r="C18">
-        <v>0.577</v>
+        <v>0.495</v>
       </c>
       <c r="D18">
-        <v>0.759</v>
+        <v>0.703</v>
       </c>
       <c r="E18">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
       <c r="F18">
-        <v>25.298</v>
+        <v>24.219</v>
       </c>
       <c r="G18">
-        <v>28.275</v>
+        <v>26.976</v>
       </c>
       <c r="H18">
-        <v>25.248</v>
+        <v>24.181</v>
       </c>
       <c r="I18">
-        <v>28.227</v>
+        <v>26.95</v>
       </c>
       <c r="J18">
-        <v>25.371</v>
+        <v>24.268</v>
       </c>
       <c r="K18">
-        <v>28.35</v>
+        <v>27.038</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1101,34 +1101,34 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>24.561</v>
+        <v>23.696</v>
       </c>
       <c r="C19">
-        <v>0.501</v>
+        <v>0.448</v>
       </c>
       <c r="D19">
-        <v>0.708</v>
+        <v>0.669</v>
       </c>
       <c r="E19">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="F19">
-        <v>23.227</v>
+        <v>22.424</v>
       </c>
       <c r="G19">
-        <v>26.001</v>
+        <v>25.048</v>
       </c>
       <c r="H19">
-        <v>23.128</v>
+        <v>22.308</v>
       </c>
       <c r="I19">
-        <v>25.96</v>
+        <v>24.973</v>
       </c>
       <c r="J19">
-        <v>23.215</v>
+        <v>22.459</v>
       </c>
       <c r="K19">
-        <v>26.047</v>
+        <v>25.124</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1141,34 +1141,34 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>24.162</v>
+        <v>22.951</v>
       </c>
       <c r="C20">
-        <v>0.978</v>
+        <v>0.45</v>
       </c>
       <c r="D20">
-        <v>0.989</v>
+        <v>0.671</v>
       </c>
       <c r="E20">
-        <v>0.031</v>
+        <v>0.021</v>
       </c>
       <c r="F20">
-        <v>22.278</v>
+        <v>21.649</v>
       </c>
       <c r="G20">
-        <v>26.155</v>
+        <v>24.278</v>
       </c>
       <c r="H20">
-        <v>21.913</v>
+        <v>21.644</v>
       </c>
       <c r="I20">
-        <v>25.914</v>
+        <v>24.231</v>
       </c>
       <c r="J20">
-        <v>22.465</v>
+        <v>21.684</v>
       </c>
       <c r="K20">
-        <v>26.465</v>
+        <v>24.271</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1181,34 +1181,34 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>23.186</v>
+        <v>22.178</v>
       </c>
       <c r="C21">
-        <v>0.488</v>
+        <v>0.404</v>
       </c>
       <c r="D21">
-        <v>0.699</v>
+        <v>0.636</v>
       </c>
       <c r="E21">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="F21">
-        <v>21.765</v>
+        <v>20.903</v>
       </c>
       <c r="G21">
-        <v>24.504</v>
+        <v>23.396</v>
       </c>
       <c r="H21">
-        <v>21.715</v>
+        <v>20.858</v>
       </c>
       <c r="I21">
-        <v>24.451</v>
+        <v>23.355</v>
       </c>
       <c r="J21">
-        <v>21.869</v>
+        <v>20.973</v>
       </c>
       <c r="K21">
-        <v>24.605</v>
+        <v>23.47</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>22.221</v>
+        <v>21.467</v>
       </c>
       <c r="C22">
-        <v>0.504</v>
+        <v>0.427</v>
       </c>
       <c r="D22">
-        <v>0.71</v>
+        <v>0.653</v>
       </c>
       <c r="E22">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="F22">
-        <v>20.806</v>
+        <v>20.185</v>
       </c>
       <c r="G22">
-        <v>23.589</v>
+        <v>22.745</v>
       </c>
       <c r="H22">
-        <v>20.733</v>
+        <v>20.091</v>
       </c>
       <c r="I22">
-        <v>23.552</v>
+        <v>22.752</v>
       </c>
       <c r="J22">
-        <v>20.867</v>
+        <v>20.18</v>
       </c>
       <c r="K22">
-        <v>23.685</v>
+        <v>22.841</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1261,34 +1261,34 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>20.437</v>
+        <v>19.707</v>
       </c>
       <c r="C23">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="D23">
-        <v>0.624</v>
+        <v>0.6</v>
       </c>
       <c r="E23">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="F23">
-        <v>19.229</v>
+        <v>18.557</v>
       </c>
       <c r="G23">
-        <v>21.675</v>
+        <v>20.91</v>
       </c>
       <c r="H23">
-        <v>19.188</v>
+        <v>18.512</v>
       </c>
       <c r="I23">
-        <v>21.673</v>
+        <v>20.886</v>
       </c>
       <c r="J23">
-        <v>19.217</v>
+        <v>18.555</v>
       </c>
       <c r="K23">
-        <v>21.701</v>
+        <v>20.929</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1301,34 +1301,34 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>20.105</v>
+        <v>19.552</v>
       </c>
       <c r="C24">
-        <v>0.441</v>
+        <v>0.414</v>
       </c>
       <c r="D24">
-        <v>0.664</v>
+        <v>0.643</v>
       </c>
       <c r="E24">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="F24">
-        <v>18.752</v>
+        <v>18.251</v>
       </c>
       <c r="G24">
-        <v>21.355</v>
+        <v>20.772</v>
       </c>
       <c r="H24">
-        <v>18.755</v>
+        <v>18.227</v>
       </c>
       <c r="I24">
-        <v>21.365</v>
+        <v>20.757</v>
       </c>
       <c r="J24">
-        <v>18.793</v>
+        <v>18.306</v>
       </c>
       <c r="K24">
-        <v>21.403</v>
+        <v>20.836</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1341,34 +1341,34 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>18.376</v>
+        <v>18.022</v>
       </c>
       <c r="C25">
-        <v>0.351</v>
+        <v>0.331</v>
       </c>
       <c r="D25">
-        <v>0.593</v>
+        <v>0.576</v>
       </c>
       <c r="E25">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="F25">
-        <v>17.205</v>
+        <v>16.887</v>
       </c>
       <c r="G25">
-        <v>19.529</v>
+        <v>19.143</v>
       </c>
       <c r="H25">
-        <v>17.228</v>
+        <v>16.935</v>
       </c>
       <c r="I25">
-        <v>19.499</v>
+        <v>19.099</v>
       </c>
       <c r="J25">
-        <v>17.244</v>
+        <v>16.938</v>
       </c>
       <c r="K25">
-        <v>19.514</v>
+        <v>19.102</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/monthly_bootstrap_combined_data_costs_users.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/monthly_bootstrap_combined_data_costs_users.xlsx
@@ -421,34 +421,34 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>257.074</v>
+        <v>274.55</v>
       </c>
       <c r="C2">
-        <v>5.839</v>
+        <v>6.707</v>
       </c>
       <c r="D2">
-        <v>2.416</v>
+        <v>2.59</v>
       </c>
       <c r="E2">
-        <v>0.076</v>
+        <v>0.082</v>
       </c>
       <c r="F2">
-        <v>252.456</v>
+        <v>269.546</v>
       </c>
       <c r="G2">
-        <v>261.928</v>
+        <v>279.698</v>
       </c>
       <c r="H2">
-        <v>252.289</v>
+        <v>269.594</v>
       </c>
       <c r="I2">
-        <v>261.758</v>
+        <v>279.535</v>
       </c>
       <c r="J2">
-        <v>252.508</v>
+        <v>269.637</v>
       </c>
       <c r="K2">
-        <v>261.977</v>
+        <v>279.578</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -461,34 +461,34 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>182.884</v>
+        <v>185.38</v>
       </c>
       <c r="C3">
-        <v>3.958</v>
+        <v>4.157</v>
       </c>
       <c r="D3">
-        <v>1.989</v>
+        <v>2.039</v>
       </c>
       <c r="E3">
-        <v>0.063</v>
+        <v>0.064</v>
       </c>
       <c r="F3">
-        <v>179.008</v>
+        <v>181.407</v>
       </c>
       <c r="G3">
-        <v>186.807</v>
+        <v>189.398</v>
       </c>
       <c r="H3">
-        <v>178.862</v>
+        <v>181.193</v>
       </c>
       <c r="I3">
-        <v>186.655</v>
+        <v>189.298</v>
       </c>
       <c r="J3">
-        <v>179.136</v>
+        <v>181.484</v>
       </c>
       <c r="K3">
-        <v>186.929</v>
+        <v>189.589</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -501,34 +501,34 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>126.795</v>
+        <v>124.044</v>
       </c>
       <c r="C4">
-        <v>2.631</v>
+        <v>2.795</v>
       </c>
       <c r="D4">
-        <v>1.622</v>
+        <v>1.672</v>
       </c>
       <c r="E4">
-        <v>0.051</v>
+        <v>0.053</v>
       </c>
       <c r="F4">
-        <v>123.661</v>
+        <v>120.816</v>
       </c>
       <c r="G4">
-        <v>130.019</v>
+        <v>127.369</v>
       </c>
       <c r="H4">
-        <v>123.529</v>
+        <v>120.555</v>
       </c>
       <c r="I4">
-        <v>129.943</v>
+        <v>127.327</v>
       </c>
       <c r="J4">
-        <v>123.692</v>
+        <v>120.811</v>
       </c>
       <c r="K4">
-        <v>130.107</v>
+        <v>127.583</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -541,34 +541,34 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>90.12</v>
+        <v>88.208</v>
       </c>
       <c r="C5">
-        <v>3.175</v>
+        <v>3.292</v>
       </c>
       <c r="D5">
-        <v>1.782</v>
+        <v>1.814</v>
       </c>
       <c r="E5">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="F5">
-        <v>86.68000000000001</v>
+        <v>84.678</v>
       </c>
       <c r="G5">
-        <v>93.666</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="H5">
-        <v>86.289</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="I5">
-        <v>93.38800000000001</v>
+        <v>91.577</v>
       </c>
       <c r="J5">
-        <v>86.90600000000001</v>
+        <v>84.864</v>
       </c>
       <c r="K5">
-        <v>94.005</v>
+        <v>92.23099999999999</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -581,34 +581,34 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>69.002</v>
+        <v>68.027</v>
       </c>
       <c r="C6">
-        <v>1.329</v>
+        <v>1.345</v>
       </c>
       <c r="D6">
-        <v>1.153</v>
+        <v>1.16</v>
       </c>
       <c r="E6">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
       <c r="F6">
-        <v>66.798</v>
+        <v>65.79900000000001</v>
       </c>
       <c r="G6">
-        <v>71.31699999999999</v>
+        <v>70.346</v>
       </c>
       <c r="H6">
-        <v>66.703</v>
+        <v>65.706</v>
       </c>
       <c r="I6">
-        <v>71.247</v>
+        <v>70.307</v>
       </c>
       <c r="J6">
-        <v>66.812</v>
+        <v>65.792</v>
       </c>
       <c r="K6">
-        <v>71.35599999999999</v>
+        <v>70.393</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -621,34 +621,34 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>55.284</v>
+        <v>55.48</v>
       </c>
       <c r="C7">
-        <v>1.065</v>
+        <v>1.157</v>
       </c>
       <c r="D7">
-        <v>1.032</v>
+        <v>1.076</v>
       </c>
       <c r="E7">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="F7">
-        <v>53.209</v>
+        <v>53.331</v>
       </c>
       <c r="G7">
-        <v>57.254</v>
+        <v>57.548</v>
       </c>
       <c r="H7">
-        <v>53.149</v>
+        <v>53.27</v>
       </c>
       <c r="I7">
-        <v>57.223</v>
+        <v>57.482</v>
       </c>
       <c r="J7">
-        <v>53.292</v>
+        <v>53.437</v>
       </c>
       <c r="K7">
-        <v>57.366</v>
+        <v>57.649</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -661,34 +661,34 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>46.587</v>
+        <v>48.142</v>
       </c>
       <c r="C8">
-        <v>0.907</v>
+        <v>1.127</v>
       </c>
       <c r="D8">
-        <v>0.952</v>
+        <v>1.062</v>
       </c>
       <c r="E8">
-        <v>0.03</v>
+        <v>0.034</v>
       </c>
       <c r="F8">
-        <v>44.732</v>
+        <v>46.063</v>
       </c>
       <c r="G8">
-        <v>48.466</v>
+        <v>50.224</v>
       </c>
       <c r="H8">
-        <v>44.667</v>
+        <v>46.006</v>
       </c>
       <c r="I8">
-        <v>48.457</v>
+        <v>50.251</v>
       </c>
       <c r="J8">
-        <v>44.729</v>
+        <v>46.034</v>
       </c>
       <c r="K8">
-        <v>48.518</v>
+        <v>50.28</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -701,34 +701,34 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>40.314</v>
+        <v>41.76</v>
       </c>
       <c r="C9">
-        <v>0.759</v>
+        <v>0.915</v>
       </c>
       <c r="D9">
-        <v>0.871</v>
+        <v>0.956</v>
       </c>
       <c r="E9">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="F9">
-        <v>38.532</v>
+        <v>39.811</v>
       </c>
       <c r="G9">
-        <v>41.948</v>
+        <v>43.56</v>
       </c>
       <c r="H9">
-        <v>38.577</v>
+        <v>39.79</v>
       </c>
       <c r="I9">
-        <v>42.03</v>
+        <v>43.658</v>
       </c>
       <c r="J9">
-        <v>38.525</v>
+        <v>39.788</v>
       </c>
       <c r="K9">
-        <v>41.977</v>
+        <v>43.656</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -741,34 +741,34 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>35.655</v>
+        <v>37.154</v>
       </c>
       <c r="C10">
-        <v>0.586</v>
+        <v>0.7</v>
       </c>
       <c r="D10">
-        <v>0.765</v>
+        <v>0.837</v>
       </c>
       <c r="E10">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="F10">
-        <v>34.077</v>
+        <v>35.446</v>
       </c>
       <c r="G10">
-        <v>37.077</v>
+        <v>38.725</v>
       </c>
       <c r="H10">
-        <v>34.023</v>
+        <v>35.424</v>
       </c>
       <c r="I10">
-        <v>37.077</v>
+        <v>38.701</v>
       </c>
       <c r="J10">
-        <v>34.156</v>
+        <v>35.539</v>
       </c>
       <c r="K10">
-        <v>37.21</v>
+        <v>38.816</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -781,34 +781,34 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>34.306</v>
+        <v>36.018</v>
       </c>
       <c r="C11">
-        <v>0.5669999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="D11">
-        <v>0.753</v>
+        <v>0.83</v>
       </c>
       <c r="E11">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="F11">
-        <v>32.789</v>
+        <v>34.352</v>
       </c>
       <c r="G11">
-        <v>35.742</v>
+        <v>37.605</v>
       </c>
       <c r="H11">
-        <v>32.705</v>
+        <v>34.22</v>
       </c>
       <c r="I11">
-        <v>35.782</v>
+        <v>37.645</v>
       </c>
       <c r="J11">
-        <v>32.79</v>
+        <v>34.352</v>
       </c>
       <c r="K11">
-        <v>35.867</v>
+        <v>37.777</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -821,34 +821,34 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>31.949</v>
+        <v>33.278</v>
       </c>
       <c r="C12">
-        <v>0.644</v>
+        <v>0.719</v>
       </c>
       <c r="D12">
-        <v>0.802</v>
+        <v>0.848</v>
       </c>
       <c r="E12">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="F12">
-        <v>30.439</v>
+        <v>31.688</v>
       </c>
       <c r="G12">
-        <v>33.583</v>
+        <v>35.013</v>
       </c>
       <c r="H12">
-        <v>30.442</v>
+        <v>31.618</v>
       </c>
       <c r="I12">
-        <v>33.447</v>
+        <v>34.949</v>
       </c>
       <c r="J12">
-        <v>30.513</v>
+        <v>31.679</v>
       </c>
       <c r="K12">
-        <v>33.518</v>
+        <v>35.01</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -861,34 +861,34 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>32.762</v>
+        <v>34.389</v>
       </c>
       <c r="C13">
-        <v>0.569</v>
+        <v>0.661</v>
       </c>
       <c r="D13">
-        <v>0.754</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E13">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="F13">
-        <v>31.295</v>
+        <v>32.803</v>
       </c>
       <c r="G13">
-        <v>34.252</v>
+        <v>35.99</v>
       </c>
       <c r="H13">
-        <v>31.313</v>
+        <v>32.757</v>
       </c>
       <c r="I13">
-        <v>34.205</v>
+        <v>35.922</v>
       </c>
       <c r="J13">
-        <v>31.33</v>
+        <v>32.864</v>
       </c>
       <c r="K13">
-        <v>34.222</v>
+        <v>36.029</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -901,34 +901,34 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>28.061</v>
+        <v>29.451</v>
       </c>
       <c r="C14">
-        <v>0.446</v>
+        <v>0.535</v>
       </c>
       <c r="D14">
-        <v>0.668</v>
+        <v>0.732</v>
       </c>
       <c r="E14">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="F14">
-        <v>26.704</v>
+        <v>27.964</v>
       </c>
       <c r="G14">
-        <v>29.323</v>
+        <v>30.831</v>
       </c>
       <c r="H14">
-        <v>26.648</v>
+        <v>27.84</v>
       </c>
       <c r="I14">
-        <v>29.319</v>
+        <v>30.815</v>
       </c>
       <c r="J14">
-        <v>26.755</v>
+        <v>28.034</v>
       </c>
       <c r="K14">
-        <v>29.426</v>
+        <v>31.009</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -941,34 +941,34 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>28.06</v>
+        <v>29.542</v>
       </c>
       <c r="C15">
-        <v>0.439</v>
+        <v>0.52</v>
       </c>
       <c r="D15">
-        <v>0.663</v>
+        <v>0.721</v>
       </c>
       <c r="E15">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="F15">
-        <v>26.738</v>
+        <v>28.095</v>
       </c>
       <c r="G15">
-        <v>29.336</v>
+        <v>30.922</v>
       </c>
       <c r="H15">
-        <v>26.755</v>
+        <v>28.014</v>
       </c>
       <c r="I15">
-        <v>29.343</v>
+        <v>30.933</v>
       </c>
       <c r="J15">
-        <v>26.754</v>
+        <v>28.117</v>
       </c>
       <c r="K15">
-        <v>29.342</v>
+        <v>31.036</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -981,34 +981,34 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>26.325</v>
+        <v>27.714</v>
       </c>
       <c r="C16">
-        <v>0.445</v>
+        <v>0.577</v>
       </c>
       <c r="D16">
-        <v>0.667</v>
+        <v>0.759</v>
       </c>
       <c r="E16">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
       <c r="F16">
-        <v>25.023</v>
+        <v>26.223</v>
       </c>
       <c r="G16">
-        <v>27.638</v>
+        <v>29.199</v>
       </c>
       <c r="H16">
-        <v>24.964</v>
+        <v>26.157</v>
       </c>
       <c r="I16">
-        <v>27.586</v>
+        <v>29.134</v>
       </c>
       <c r="J16">
-        <v>25.07</v>
+        <v>26.292</v>
       </c>
       <c r="K16">
-        <v>27.691</v>
+        <v>29.269</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1021,34 +1021,34 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>26.472</v>
+        <v>27.36</v>
       </c>
       <c r="C17">
-        <v>0.552</v>
+        <v>0.576</v>
       </c>
       <c r="D17">
-        <v>0.743</v>
+        <v>0.759</v>
       </c>
       <c r="E17">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="F17">
-        <v>24.986</v>
+        <v>25.859</v>
       </c>
       <c r="G17">
-        <v>27.899</v>
+        <v>28.833</v>
       </c>
       <c r="H17">
-        <v>24.974</v>
+        <v>25.874</v>
       </c>
       <c r="I17">
-        <v>27.802</v>
+        <v>28.769</v>
       </c>
       <c r="J17">
-        <v>25.113</v>
+        <v>25.937</v>
       </c>
       <c r="K17">
-        <v>27.94</v>
+        <v>28.832</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1061,34 +1061,34 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>25.621</v>
+        <v>26.996</v>
       </c>
       <c r="C18">
-        <v>0.495</v>
+        <v>0.575</v>
       </c>
       <c r="D18">
-        <v>0.703</v>
+        <v>0.758</v>
       </c>
       <c r="E18">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="F18">
-        <v>24.219</v>
+        <v>25.482</v>
       </c>
       <c r="G18">
-        <v>26.976</v>
+        <v>28.455</v>
       </c>
       <c r="H18">
-        <v>24.181</v>
+        <v>25.433</v>
       </c>
       <c r="I18">
-        <v>26.95</v>
+        <v>28.378</v>
       </c>
       <c r="J18">
-        <v>24.268</v>
+        <v>25.587</v>
       </c>
       <c r="K18">
-        <v>27.038</v>
+        <v>28.532</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1101,34 +1101,34 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>23.696</v>
+        <v>24.788</v>
       </c>
       <c r="C19">
-        <v>0.448</v>
+        <v>0.502</v>
       </c>
       <c r="D19">
-        <v>0.669</v>
+        <v>0.709</v>
       </c>
       <c r="E19">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="F19">
-        <v>22.424</v>
+        <v>23.449</v>
       </c>
       <c r="G19">
-        <v>25.048</v>
+        <v>26.227</v>
       </c>
       <c r="H19">
-        <v>22.308</v>
+        <v>23.33</v>
       </c>
       <c r="I19">
-        <v>24.973</v>
+        <v>26.192</v>
       </c>
       <c r="J19">
-        <v>22.459</v>
+        <v>23.434</v>
       </c>
       <c r="K19">
-        <v>25.124</v>
+        <v>26.296</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1141,34 +1141,34 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>22.951</v>
+        <v>24.211</v>
       </c>
       <c r="C20">
-        <v>0.45</v>
+        <v>0.768</v>
       </c>
       <c r="D20">
-        <v>0.671</v>
+        <v>0.876</v>
       </c>
       <c r="E20">
-        <v>0.021</v>
+        <v>0.028</v>
       </c>
       <c r="F20">
-        <v>21.649</v>
+        <v>22.532</v>
       </c>
       <c r="G20">
-        <v>24.278</v>
+        <v>25.967</v>
       </c>
       <c r="H20">
-        <v>21.644</v>
+        <v>22.337</v>
       </c>
       <c r="I20">
-        <v>24.231</v>
+        <v>25.83</v>
       </c>
       <c r="J20">
-        <v>21.684</v>
+        <v>22.631</v>
       </c>
       <c r="K20">
-        <v>24.271</v>
+        <v>26.124</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1181,34 +1181,34 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>22.178</v>
+        <v>23.368</v>
       </c>
       <c r="C21">
-        <v>0.404</v>
+        <v>0.481</v>
       </c>
       <c r="D21">
-        <v>0.636</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="E21">
-        <v>0.02</v>
+        <v>0.022</v>
       </c>
       <c r="F21">
-        <v>20.903</v>
+        <v>21.966</v>
       </c>
       <c r="G21">
-        <v>23.396</v>
+        <v>24.684</v>
       </c>
       <c r="H21">
-        <v>20.858</v>
+        <v>21.942</v>
       </c>
       <c r="I21">
-        <v>23.355</v>
+        <v>24.65</v>
       </c>
       <c r="J21">
-        <v>20.973</v>
+        <v>22.042</v>
       </c>
       <c r="K21">
-        <v>23.47</v>
+        <v>24.75</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>21.467</v>
+        <v>22.432</v>
       </c>
       <c r="C22">
-        <v>0.427</v>
+        <v>0.502</v>
       </c>
       <c r="D22">
-        <v>0.653</v>
+        <v>0.708</v>
       </c>
       <c r="E22">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="F22">
-        <v>20.185</v>
+        <v>21.025</v>
       </c>
       <c r="G22">
-        <v>22.745</v>
+        <v>23.802</v>
       </c>
       <c r="H22">
-        <v>20.091</v>
+        <v>20.92</v>
       </c>
       <c r="I22">
-        <v>22.752</v>
+        <v>23.763</v>
       </c>
       <c r="J22">
-        <v>20.18</v>
+        <v>21.082</v>
       </c>
       <c r="K22">
-        <v>22.841</v>
+        <v>23.926</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1261,34 +1261,34 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>19.707</v>
+        <v>20.65</v>
       </c>
       <c r="C23">
-        <v>0.36</v>
+        <v>0.398</v>
       </c>
       <c r="D23">
-        <v>0.6</v>
+        <v>0.631</v>
       </c>
       <c r="E23">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="F23">
-        <v>18.557</v>
+        <v>19.431</v>
       </c>
       <c r="G23">
-        <v>20.91</v>
+        <v>21.905</v>
       </c>
       <c r="H23">
-        <v>18.512</v>
+        <v>19.371</v>
       </c>
       <c r="I23">
-        <v>20.886</v>
+        <v>21.885</v>
       </c>
       <c r="J23">
-        <v>18.555</v>
+        <v>19.433</v>
       </c>
       <c r="K23">
-        <v>20.929</v>
+        <v>21.947</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1301,34 +1301,34 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>19.552</v>
+        <v>20.328</v>
       </c>
       <c r="C24">
-        <v>0.414</v>
+        <v>0.452</v>
       </c>
       <c r="D24">
-        <v>0.643</v>
+        <v>0.672</v>
       </c>
       <c r="E24">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="F24">
-        <v>18.251</v>
+        <v>18.958</v>
       </c>
       <c r="G24">
-        <v>20.772</v>
+        <v>21.593</v>
       </c>
       <c r="H24">
-        <v>18.227</v>
+        <v>18.959</v>
       </c>
       <c r="I24">
-        <v>20.757</v>
+        <v>21.626</v>
       </c>
       <c r="J24">
-        <v>18.306</v>
+        <v>18.977</v>
       </c>
       <c r="K24">
-        <v>20.836</v>
+        <v>21.644</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1341,34 +1341,34 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>18.022</v>
+        <v>18.574</v>
       </c>
       <c r="C25">
-        <v>0.331</v>
+        <v>0.358</v>
       </c>
       <c r="D25">
-        <v>0.576</v>
+        <v>0.599</v>
       </c>
       <c r="E25">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="F25">
-        <v>16.887</v>
+        <v>17.384</v>
       </c>
       <c r="G25">
-        <v>19.143</v>
+        <v>19.731</v>
       </c>
       <c r="H25">
-        <v>16.935</v>
+        <v>17.405</v>
       </c>
       <c r="I25">
-        <v>19.099</v>
+        <v>19.665</v>
       </c>
       <c r="J25">
-        <v>16.938</v>
+        <v>17.466</v>
       </c>
       <c r="K25">
-        <v>19.102</v>
+        <v>19.726</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/monthly_bootstrap_combined_data_costs_users.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/monthly_bootstrap_combined_data_costs_users.xlsx
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="B26">
-        <v>295.616</v>
+        <v>281.966</v>
       </c>
       <c r="C26">
-        <v>6.471</v>
+        <v>6.077</v>
       </c>
       <c r="D26">
-        <v>2.544</v>
+        <v>2.465</v>
       </c>
       <c r="E26">
-        <v>0.08</v>
+        <v>0.078</v>
       </c>
       <c r="F26">
-        <v>290.896</v>
+        <v>277.345</v>
       </c>
       <c r="G26">
-        <v>300.868</v>
+        <v>287.009</v>
       </c>
       <c r="H26">
-        <v>290.826</v>
+        <v>277</v>
       </c>
       <c r="I26">
-        <v>300.924</v>
+        <v>287.166</v>
       </c>
       <c r="J26">
-        <v>290.574</v>
+        <v>276.977</v>
       </c>
       <c r="K26">
-        <v>300.672</v>
+        <v>287.142</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1421,34 +1421,34 @@
         <v>2</v>
       </c>
       <c r="B27">
-        <v>191.34</v>
+        <v>200.671</v>
       </c>
       <c r="C27">
-        <v>3.751</v>
+        <v>4.71</v>
       </c>
       <c r="D27">
-        <v>1.937</v>
+        <v>2.17</v>
       </c>
       <c r="E27">
-        <v>0.061</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F27">
-        <v>187.277</v>
+        <v>196.219</v>
       </c>
       <c r="G27">
-        <v>194.869</v>
+        <v>204.726</v>
       </c>
       <c r="H27">
-        <v>187.315</v>
+        <v>196.148</v>
       </c>
       <c r="I27">
-        <v>194.882</v>
+        <v>204.43</v>
       </c>
       <c r="J27">
-        <v>187.531</v>
+        <v>196.714</v>
       </c>
       <c r="K27">
-        <v>195.098</v>
+        <v>204.996</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1461,34 +1461,34 @@
         <v>3</v>
       </c>
       <c r="B28">
-        <v>127.49</v>
+        <v>137.177</v>
       </c>
       <c r="C28">
-        <v>2.798</v>
+        <v>3.076</v>
       </c>
       <c r="D28">
-        <v>1.673</v>
+        <v>1.754</v>
       </c>
       <c r="E28">
-        <v>0.053</v>
+        <v>0.055</v>
       </c>
       <c r="F28">
-        <v>124.098</v>
+        <v>133.593</v>
       </c>
       <c r="G28">
-        <v>130.655</v>
+        <v>140.468</v>
       </c>
       <c r="H28">
-        <v>124.07</v>
+        <v>133.744</v>
       </c>
       <c r="I28">
-        <v>130.675</v>
+        <v>140.511</v>
       </c>
       <c r="J28">
-        <v>124.191</v>
+        <v>133.697</v>
       </c>
       <c r="K28">
-        <v>130.796</v>
+        <v>140.463</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1501,34 +1501,34 @@
         <v>4</v>
       </c>
       <c r="B29">
-        <v>90.39400000000001</v>
+        <v>95.988</v>
       </c>
       <c r="C29">
-        <v>2.76</v>
+        <v>2.301</v>
       </c>
       <c r="D29">
-        <v>1.661</v>
+        <v>1.517</v>
       </c>
       <c r="E29">
-        <v>0.053</v>
+        <v>0.048</v>
       </c>
       <c r="F29">
-        <v>87.074</v>
+        <v>92.986</v>
       </c>
       <c r="G29">
-        <v>93.587</v>
+        <v>98.932</v>
       </c>
       <c r="H29">
-        <v>86.904</v>
+        <v>92.81399999999999</v>
       </c>
       <c r="I29">
-        <v>93.39</v>
+        <v>98.82899999999999</v>
       </c>
       <c r="J29">
-        <v>87.334</v>
+        <v>93.11799999999999</v>
       </c>
       <c r="K29">
-        <v>93.81999999999999</v>
+        <v>99.133</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1541,34 +1541,34 @@
         <v>5</v>
       </c>
       <c r="B30">
-        <v>70.218</v>
+        <v>73.449</v>
       </c>
       <c r="C30">
-        <v>1.369</v>
+        <v>1.589</v>
       </c>
       <c r="D30">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="E30">
-        <v>0.037</v>
+        <v>0.04</v>
       </c>
       <c r="F30">
-        <v>67.88200000000001</v>
+        <v>71.021</v>
       </c>
       <c r="G30">
-        <v>72.46899999999999</v>
+        <v>75.961</v>
       </c>
       <c r="H30">
-        <v>67.80200000000001</v>
+        <v>70.92400000000001</v>
       </c>
       <c r="I30">
-        <v>72.387</v>
+        <v>75.839</v>
       </c>
       <c r="J30">
-        <v>68.006</v>
+        <v>71.101</v>
       </c>
       <c r="K30">
-        <v>72.59099999999999</v>
+        <v>76.015</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1581,34 +1581,34 @@
         <v>6</v>
       </c>
       <c r="B31">
-        <v>56.836</v>
+        <v>58.314</v>
       </c>
       <c r="C31">
-        <v>1.081</v>
+        <v>1.164</v>
       </c>
       <c r="D31">
-        <v>1.04</v>
+        <v>1.079</v>
       </c>
       <c r="E31">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="F31">
-        <v>54.876</v>
+        <v>56.291</v>
       </c>
       <c r="G31">
-        <v>58.952</v>
+        <v>60.521</v>
       </c>
       <c r="H31">
-        <v>54.874</v>
+        <v>56.239</v>
       </c>
       <c r="I31">
-        <v>59.028</v>
+        <v>60.581</v>
       </c>
       <c r="J31">
-        <v>54.721</v>
+        <v>56.139</v>
       </c>
       <c r="K31">
-        <v>58.875</v>
+        <v>60.48</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -1621,34 +1621,34 @@
         <v>7</v>
       </c>
       <c r="B32">
-        <v>49.298</v>
+        <v>49.036</v>
       </c>
       <c r="C32">
-        <v>1.004</v>
+        <v>0.978</v>
       </c>
       <c r="D32">
-        <v>1.002</v>
+        <v>0.989</v>
       </c>
       <c r="E32">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="F32">
-        <v>47.407</v>
+        <v>47.151</v>
       </c>
       <c r="G32">
-        <v>51.334</v>
+        <v>51.027</v>
       </c>
       <c r="H32">
-        <v>47.414</v>
+        <v>47.108</v>
       </c>
       <c r="I32">
-        <v>51.277</v>
+        <v>50.974</v>
       </c>
       <c r="J32">
-        <v>47.391</v>
+        <v>47.151</v>
       </c>
       <c r="K32">
-        <v>51.255</v>
+        <v>51.017</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -1661,34 +1661,34 @@
         <v>8</v>
       </c>
       <c r="B33">
-        <v>42.955</v>
+        <v>41.678</v>
       </c>
       <c r="C33">
-        <v>0.928</v>
+        <v>0.872</v>
       </c>
       <c r="D33">
-        <v>0.964</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="E33">
         <v>0.03</v>
       </c>
       <c r="F33">
-        <v>41.092</v>
+        <v>39.859</v>
       </c>
       <c r="G33">
-        <v>44.869</v>
+        <v>43.519</v>
       </c>
       <c r="H33">
-        <v>41.033</v>
+        <v>39.764</v>
       </c>
       <c r="I33">
-        <v>44.763</v>
+        <v>43.393</v>
       </c>
       <c r="J33">
-        <v>41.171</v>
+        <v>39.974</v>
       </c>
       <c r="K33">
-        <v>44.902</v>
+        <v>43.603</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -1701,34 +1701,34 @@
         <v>9</v>
       </c>
       <c r="B34">
-        <v>38.388</v>
+        <v>37.478</v>
       </c>
       <c r="C34">
-        <v>0.779</v>
+        <v>0.71</v>
       </c>
       <c r="D34">
-        <v>0.882</v>
+        <v>0.842</v>
       </c>
       <c r="E34">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="F34">
-        <v>36.625</v>
+        <v>35.799</v>
       </c>
       <c r="G34">
-        <v>40.084</v>
+        <v>39.102</v>
       </c>
       <c r="H34">
-        <v>36.743</v>
+        <v>35.767</v>
       </c>
       <c r="I34">
-        <v>40.151</v>
+        <v>39.177</v>
       </c>
       <c r="J34">
-        <v>36.591</v>
+        <v>35.751</v>
       </c>
       <c r="K34">
-        <v>39.999</v>
+        <v>39.162</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -1741,34 +1741,34 @@
         <v>10</v>
       </c>
       <c r="B35">
-        <v>36.886</v>
+        <v>35.479</v>
       </c>
       <c r="C35">
-        <v>0.751</v>
+        <v>0.696</v>
       </c>
       <c r="D35">
-        <v>0.866</v>
+        <v>0.834</v>
       </c>
       <c r="E35">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="F35">
-        <v>35.23</v>
+        <v>33.858</v>
       </c>
       <c r="G35">
-        <v>38.627</v>
+        <v>37.128</v>
       </c>
       <c r="H35">
-        <v>35.202</v>
+        <v>33.794</v>
       </c>
       <c r="I35">
-        <v>38.59</v>
+        <v>37.109</v>
       </c>
       <c r="J35">
-        <v>35.225</v>
+        <v>33.862</v>
       </c>
       <c r="K35">
-        <v>38.613</v>
+        <v>37.178</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -1781,34 +1781,34 @@
         <v>11</v>
       </c>
       <c r="B36">
-        <v>34.472</v>
+        <v>33.371</v>
       </c>
       <c r="C36">
-        <v>0.77</v>
+        <v>0.838</v>
       </c>
       <c r="D36">
-        <v>0.877</v>
+        <v>0.915</v>
       </c>
       <c r="E36">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="F36">
-        <v>32.823</v>
+        <v>31.692</v>
       </c>
       <c r="G36">
-        <v>36.262</v>
+        <v>35.28</v>
       </c>
       <c r="H36">
-        <v>32.653</v>
+        <v>31.436</v>
       </c>
       <c r="I36">
-        <v>36.228</v>
+        <v>35.242</v>
       </c>
       <c r="J36">
-        <v>32.787</v>
+        <v>31.615</v>
       </c>
       <c r="K36">
-        <v>36.362</v>
+        <v>35.421</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -1821,34 +1821,34 @@
         <v>12</v>
       </c>
       <c r="B37">
-        <v>35.508</v>
+        <v>34.096</v>
       </c>
       <c r="C37">
-        <v>0.754</v>
+        <v>0.701</v>
       </c>
       <c r="D37">
-        <v>0.868</v>
+        <v>0.837</v>
       </c>
       <c r="E37">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="F37">
-        <v>33.792</v>
+        <v>32.482</v>
       </c>
       <c r="G37">
-        <v>37.195</v>
+        <v>35.763</v>
       </c>
       <c r="H37">
-        <v>33.736</v>
+        <v>32.572</v>
       </c>
       <c r="I37">
-        <v>37.139</v>
+        <v>35.754</v>
       </c>
       <c r="J37">
-        <v>33.863</v>
+        <v>32.465</v>
       </c>
       <c r="K37">
-        <v>37.266</v>
+        <v>35.646</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -1861,34 +1861,34 @@
         <v>13</v>
       </c>
       <c r="B38">
-        <v>30.006</v>
+        <v>28.859</v>
       </c>
       <c r="C38">
-        <v>0.5659999999999999</v>
+        <v>0.514</v>
       </c>
       <c r="D38">
-        <v>0.752</v>
+        <v>0.717</v>
       </c>
       <c r="E38">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="F38">
-        <v>28.625</v>
+        <v>27.547</v>
       </c>
       <c r="G38">
-        <v>31.573</v>
+        <v>30.358</v>
       </c>
       <c r="H38">
-        <v>28.568</v>
+        <v>27.501</v>
       </c>
       <c r="I38">
-        <v>31.617</v>
+        <v>30.304</v>
       </c>
       <c r="J38">
-        <v>28.488</v>
+        <v>27.508</v>
       </c>
       <c r="K38">
-        <v>31.537</v>
+        <v>30.311</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -1901,34 +1901,34 @@
         <v>14</v>
       </c>
       <c r="B39">
-        <v>30.641</v>
+        <v>29.002</v>
       </c>
       <c r="C39">
-        <v>0.627</v>
+        <v>0.543</v>
       </c>
       <c r="D39">
-        <v>0.792</v>
+        <v>0.737</v>
       </c>
       <c r="E39">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="F39">
-        <v>29.189</v>
+        <v>27.659</v>
       </c>
       <c r="G39">
-        <v>32.292</v>
+        <v>30.546</v>
       </c>
       <c r="H39">
-        <v>29.085</v>
+        <v>27.543</v>
       </c>
       <c r="I39">
-        <v>32.252</v>
+        <v>30.514</v>
       </c>
       <c r="J39">
-        <v>29.129</v>
+        <v>27.591</v>
       </c>
       <c r="K39">
-        <v>32.296</v>
+        <v>30.562</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -1941,34 +1941,34 @@
         <v>15</v>
       </c>
       <c r="B40">
-        <v>28.701</v>
+        <v>27.551</v>
       </c>
       <c r="C40">
-        <v>0.595</v>
+        <v>0.53</v>
       </c>
       <c r="D40">
-        <v>0.772</v>
+        <v>0.728</v>
       </c>
       <c r="E40">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="F40">
-        <v>27.198</v>
+        <v>26.129</v>
       </c>
       <c r="G40">
-        <v>30.223</v>
+        <v>28.983</v>
       </c>
       <c r="H40">
-        <v>27.122</v>
+        <v>26.134</v>
       </c>
       <c r="I40">
-        <v>30.203</v>
+        <v>28.947</v>
       </c>
       <c r="J40">
-        <v>27.208</v>
+        <v>26.161</v>
       </c>
       <c r="K40">
-        <v>30.289</v>
+        <v>28.973</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -1981,34 +1981,34 @@
         <v>16</v>
       </c>
       <c r="B41">
-        <v>28.285</v>
+        <v>27.144</v>
       </c>
       <c r="C41">
-        <v>0.595</v>
+        <v>0.599</v>
       </c>
       <c r="D41">
-        <v>0.771</v>
+        <v>0.774</v>
       </c>
       <c r="E41">
         <v>0.024</v>
       </c>
       <c r="F41">
-        <v>26.72</v>
+        <v>25.569</v>
       </c>
       <c r="G41">
-        <v>29.743</v>
+        <v>28.603</v>
       </c>
       <c r="H41">
-        <v>26.699</v>
+        <v>25.533</v>
       </c>
       <c r="I41">
-        <v>29.676</v>
+        <v>28.533</v>
       </c>
       <c r="J41">
-        <v>26.841</v>
+        <v>25.698</v>
       </c>
       <c r="K41">
-        <v>29.818</v>
+        <v>28.697</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2021,34 +2021,34 @@
         <v>17</v>
       </c>
       <c r="B42">
-        <v>28.13</v>
+        <v>26.597</v>
       </c>
       <c r="C42">
-        <v>0.585</v>
+        <v>0.525</v>
       </c>
       <c r="D42">
-        <v>0.765</v>
+        <v>0.725</v>
       </c>
       <c r="E42">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="F42">
-        <v>26.673</v>
+        <v>25.161</v>
       </c>
       <c r="G42">
-        <v>29.671</v>
+        <v>28.002</v>
       </c>
       <c r="H42">
-        <v>26.715</v>
+        <v>25.062</v>
       </c>
       <c r="I42">
-        <v>29.612</v>
+        <v>27.954</v>
       </c>
       <c r="J42">
-        <v>26.69</v>
+        <v>25.224</v>
       </c>
       <c r="K42">
-        <v>29.587</v>
+        <v>28.117</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2061,34 +2061,34 @@
         <v>18</v>
       </c>
       <c r="B43">
-        <v>25.578</v>
+        <v>24.527</v>
       </c>
       <c r="C43">
-        <v>0.527</v>
+        <v>0.49</v>
       </c>
       <c r="D43">
-        <v>0.726</v>
+        <v>0.7</v>
       </c>
       <c r="E43">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="F43">
-        <v>24.14</v>
+        <v>23.132</v>
       </c>
       <c r="G43">
-        <v>26.984</v>
+        <v>25.876</v>
       </c>
       <c r="H43">
-        <v>24.091</v>
+        <v>23.079</v>
       </c>
       <c r="I43">
-        <v>26.935</v>
+        <v>25.86</v>
       </c>
       <c r="J43">
-        <v>24.205</v>
+        <v>23.17</v>
       </c>
       <c r="K43">
-        <v>27.049</v>
+        <v>25.951</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2101,34 +2101,34 @@
         <v>19</v>
       </c>
       <c r="B44">
-        <v>25.204</v>
+        <v>23.996</v>
       </c>
       <c r="C44">
-        <v>0.964</v>
+        <v>0.489</v>
       </c>
       <c r="D44">
-        <v>0.982</v>
+        <v>0.699</v>
       </c>
       <c r="E44">
-        <v>0.031</v>
+        <v>0.022</v>
       </c>
       <c r="F44">
-        <v>23.345</v>
+        <v>22.678</v>
       </c>
       <c r="G44">
-        <v>27.194</v>
+        <v>25.419</v>
       </c>
       <c r="H44">
-        <v>23.176</v>
+        <v>22.706</v>
       </c>
       <c r="I44">
-        <v>27.031</v>
+        <v>25.415</v>
       </c>
       <c r="J44">
-        <v>23.443</v>
+        <v>22.63</v>
       </c>
       <c r="K44">
-        <v>27.297</v>
+        <v>25.339</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2141,34 +2141,34 @@
         <v>20</v>
       </c>
       <c r="B45">
-        <v>24.095</v>
+        <v>23.382</v>
       </c>
       <c r="C45">
-        <v>0.506</v>
+        <v>0.494</v>
       </c>
       <c r="D45">
-        <v>0.711</v>
+        <v>0.703</v>
       </c>
       <c r="E45">
         <v>0.022</v>
       </c>
       <c r="F45">
-        <v>22.676</v>
+        <v>21.974</v>
       </c>
       <c r="G45">
-        <v>25.464</v>
+        <v>24.73</v>
       </c>
       <c r="H45">
-        <v>22.67</v>
+        <v>21.932</v>
       </c>
       <c r="I45">
-        <v>25.418</v>
+        <v>24.715</v>
       </c>
       <c r="J45">
-        <v>22.747</v>
+        <v>22.019</v>
       </c>
       <c r="K45">
-        <v>25.495</v>
+        <v>24.802</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2181,34 +2181,34 @@
         <v>21</v>
       </c>
       <c r="B46">
-        <v>23.398</v>
+        <v>22.879</v>
       </c>
       <c r="C46">
-        <v>0.513</v>
+        <v>0.525</v>
       </c>
       <c r="D46">
-        <v>0.716</v>
+        <v>0.725</v>
       </c>
       <c r="E46">
         <v>0.023</v>
       </c>
       <c r="F46">
-        <v>21.965</v>
+        <v>21.406</v>
       </c>
       <c r="G46">
-        <v>24.773</v>
+        <v>24.247</v>
       </c>
       <c r="H46">
-        <v>21.929</v>
+        <v>21.359</v>
       </c>
       <c r="I46">
-        <v>24.718</v>
+        <v>24.215</v>
       </c>
       <c r="J46">
-        <v>22.05</v>
+        <v>21.491</v>
       </c>
       <c r="K46">
-        <v>24.839</v>
+        <v>24.346</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2221,34 +2221,34 @@
         <v>22</v>
       </c>
       <c r="B47">
-        <v>21.165</v>
+        <v>20.507</v>
       </c>
       <c r="C47">
-        <v>0.43</v>
+        <v>0.472</v>
       </c>
       <c r="D47">
-        <v>0.655</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="E47">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="F47">
-        <v>19.941</v>
+        <v>19.219</v>
       </c>
       <c r="G47">
-        <v>22.511</v>
+        <v>21.911</v>
       </c>
       <c r="H47">
-        <v>20.01</v>
+        <v>19.257</v>
       </c>
       <c r="I47">
-        <v>22.48</v>
+        <v>21.906</v>
       </c>
       <c r="J47">
-        <v>19.911</v>
+        <v>19.165</v>
       </c>
       <c r="K47">
-        <v>22.381</v>
+        <v>21.814</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2261,34 +2261,34 @@
         <v>23</v>
       </c>
       <c r="B48">
-        <v>20.988</v>
+        <v>20.425</v>
       </c>
       <c r="C48">
-        <v>0.492</v>
+        <v>0.473</v>
       </c>
       <c r="D48">
-        <v>0.702</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="E48">
         <v>0.022</v>
       </c>
       <c r="F48">
-        <v>19.564</v>
+        <v>19.027</v>
       </c>
       <c r="G48">
-        <v>22.314</v>
+        <v>21.723</v>
       </c>
       <c r="H48">
-        <v>19.55</v>
+        <v>18.981</v>
       </c>
       <c r="I48">
-        <v>22.224</v>
+        <v>21.59</v>
       </c>
       <c r="J48">
-        <v>19.703</v>
+        <v>19.211</v>
       </c>
       <c r="K48">
-        <v>22.377</v>
+        <v>21.819</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2301,34 +2301,34 @@
         <v>24</v>
       </c>
       <c r="B49">
-        <v>19.056</v>
+        <v>18.905</v>
       </c>
       <c r="C49">
-        <v>0.352</v>
+        <v>0.4</v>
       </c>
       <c r="D49">
-        <v>0.593</v>
+        <v>0.632</v>
       </c>
       <c r="E49">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="F49">
-        <v>17.867</v>
+        <v>17.617</v>
       </c>
       <c r="G49">
-        <v>20.192</v>
+        <v>20.096</v>
       </c>
       <c r="H49">
-        <v>17.708</v>
+        <v>17.515</v>
       </c>
       <c r="I49">
-        <v>20.165</v>
+        <v>20.122</v>
       </c>
       <c r="J49">
-        <v>17.92</v>
+        <v>17.64</v>
       </c>
       <c r="K49">
-        <v>20.377</v>
+        <v>20.247</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
